--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,16 +435,51 @@
         <v>担当者</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>#1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026/9/25 5:30:23</v>
+      </c>
+      <c r="D2" t="str">
+        <v>モンブラン×1, チョコケーキ×1, オレンジジュース×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E2">
+        <v>800</v>
+      </c>
+      <c r="F2">
+        <v>200</v>
+      </c>
+      <c r="G2">
+        <v>600</v>
+      </c>
+      <c r="H2">
+        <v>1000</v>
+      </c>
+      <c r="I2">
+        <v>400</v>
+      </c>
+      <c r="J2" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K2" t="str">
+        <v>いち</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -472,9 +507,113 @@
         <v>担当者</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>#1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026/9/25 5:30:23</v>
+      </c>
+      <c r="D2" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E2">
+        <v>200</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>200</v>
+      </c>
+      <c r="H2" t="str">
+        <v>いち</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>#1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026/9/25 5:30:23</v>
+      </c>
+      <c r="D3" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E3">
+        <v>200</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>200</v>
+      </c>
+      <c r="H3" t="str">
+        <v>いち</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>#1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026/9/25 5:30:23</v>
+      </c>
+      <c r="D4" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E4">
+        <v>200</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>200</v>
+      </c>
+      <c r="H4" t="str">
+        <v>いち</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>#1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026/9/25 5:30:23</v>
+      </c>
+      <c r="D5" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E5">
+        <v>200</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>200</v>
+      </c>
+      <c r="H5" t="str">
+        <v>いち</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -470,16 +470,51 @@
         <v>いち</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>#2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026/9/25 5:32:23</v>
+      </c>
+      <c r="D3" t="str">
+        <v>クリームチーズタルト×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E3">
+        <v>400</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <v>300</v>
+      </c>
+      <c r="H3">
+        <v>500</v>
+      </c>
+      <c r="I3">
+        <v>200</v>
+      </c>
+      <c r="J3" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K3" t="str">
+        <v>いち</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -611,9 +646,61 @@
         <v>いち</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>#2</v>
+      </c>
+      <c r="B6" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026/9/25 5:32:23</v>
+      </c>
+      <c r="D6" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E6">
+        <v>200</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>200</v>
+      </c>
+      <c r="H6" t="str">
+        <v>いち</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>#2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C7" t="str">
+        <v>2026/9/25 5:32:23</v>
+      </c>
+      <c r="D7" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E7">
+        <v>200</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>200</v>
+      </c>
+      <c r="H7" t="str">
+        <v>いち</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -505,16 +505,51 @@
         <v>いち</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>#3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026/9/25 5:34:44</v>
+      </c>
+      <c r="D4" t="str">
+        <v>クリームチーズタルト×1, プリンアラモード×1, Hot紅茶×1</v>
+      </c>
+      <c r="E4">
+        <v>600</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>500</v>
+      </c>
+      <c r="H4">
+        <v>500</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K4" t="str">
+        <v>いちiPad</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -698,9 +733,87 @@
         <v>いち</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>#3</v>
+      </c>
+      <c r="B8" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C8" t="str">
+        <v>2026/9/25 5:34:44</v>
+      </c>
+      <c r="D8" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E8">
+        <v>200</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>200</v>
+      </c>
+      <c r="H8" t="str">
+        <v>いちiPad</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>#3</v>
+      </c>
+      <c r="B9" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2026/9/25 5:34:44</v>
+      </c>
+      <c r="D9" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E9">
+        <v>200</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>200</v>
+      </c>
+      <c r="H9" t="str">
+        <v>いちiPad</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>#3</v>
+      </c>
+      <c r="B10" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2026/9/25 5:34:44</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Hot紅茶</v>
+      </c>
+      <c r="E10">
+        <v>200</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>200</v>
+      </c>
+      <c r="H10" t="str">
+        <v>いちiPad</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -464,7 +464,7 @@
         <v>400</v>
       </c>
       <c r="J2" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K2" t="str">
         <v>いち</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -540,16 +540,86 @@
         <v>いちiPad</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>#4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026/9/25 6:21:18</v>
+      </c>
+      <c r="D5" t="str">
+        <v>マカロン×1, プリンアラモード×1, Hot紅茶×1, Iceココア×1</v>
+      </c>
+      <c r="E5">
+        <v>800</v>
+      </c>
+      <c r="F5">
+        <v>200</v>
+      </c>
+      <c r="G5">
+        <v>600</v>
+      </c>
+      <c r="H5">
+        <v>1000</v>
+      </c>
+      <c r="I5">
+        <v>400</v>
+      </c>
+      <c r="J5" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K5" t="str">
+        <v>いちiPad</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>#5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026/9/25 6:26:39</v>
+      </c>
+      <c r="D6" t="str">
+        <v>オレンジジュース×1</v>
+      </c>
+      <c r="E6">
+        <v>200</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>200</v>
+      </c>
+      <c r="H6">
+        <v>200</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K6" t="str">
+        <v>いちiPad</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -811,9 +881,139 @@
         <v>いちiPad</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>#4</v>
+      </c>
+      <c r="B11" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026/9/25 6:21:18</v>
+      </c>
+      <c r="D11" t="str">
+        <v>マカロン</v>
+      </c>
+      <c r="E11">
+        <v>200</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>200</v>
+      </c>
+      <c r="H11" t="str">
+        <v>いちiPad</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>#4</v>
+      </c>
+      <c r="B12" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026/9/25 6:21:18</v>
+      </c>
+      <c r="D12" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E12">
+        <v>200</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>200</v>
+      </c>
+      <c r="H12" t="str">
+        <v>いちiPad</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>#4</v>
+      </c>
+      <c r="B13" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2026/9/25 6:21:18</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Hot紅茶</v>
+      </c>
+      <c r="E13">
+        <v>200</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>200</v>
+      </c>
+      <c r="H13" t="str">
+        <v>いちiPad</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>#4</v>
+      </c>
+      <c r="B14" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026/9/25 6:21:18</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E14">
+        <v>200</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>200</v>
+      </c>
+      <c r="H14" t="str">
+        <v>いちiPad</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>#5</v>
+      </c>
+      <c r="B15" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026/9/25 6:26:39</v>
+      </c>
+      <c r="D15" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E15">
+        <v>200</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>200</v>
+      </c>
+      <c r="H15" t="str">
+        <v>いちiPad</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -610,16 +610,51 @@
         <v>いちiPad</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>#6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C7" t="str">
+        <v>2026/9/25 6:44:09</v>
+      </c>
+      <c r="D7" t="str">
+        <v>カラメルカスタード×1, オレンジジュース×1</v>
+      </c>
+      <c r="E7">
+        <v>400</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>300</v>
+      </c>
+      <c r="H7">
+        <v>500</v>
+      </c>
+      <c r="I7">
+        <v>200</v>
+      </c>
+      <c r="J7" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K7" t="str">
+        <v>いち</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1011,9 +1046,61 @@
         <v>いちiPad</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>#6</v>
+      </c>
+      <c r="B16" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026/9/25 6:44:09</v>
+      </c>
+      <c r="D16" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E16">
+        <v>200</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>200</v>
+      </c>
+      <c r="H16" t="str">
+        <v>いち</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>#6</v>
+      </c>
+      <c r="B17" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026/9/25 6:44:09</v>
+      </c>
+      <c r="D17" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E17">
+        <v>200</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>200</v>
+      </c>
+      <c r="H17" t="str">
+        <v>いち</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -499,7 +499,7 @@
         <v>200</v>
       </c>
       <c r="J3" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K3" t="str">
         <v>いち</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -645,16 +645,51 @@
         <v>いち</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>#7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C8" t="str">
+        <v>2026/9/25 11:10:04</v>
+      </c>
+      <c r="D8" t="str">
+        <v>モンブラン×1, Iceココア×1</v>
+      </c>
+      <c r="E8">
+        <v>400</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>300</v>
+      </c>
+      <c r="H8">
+        <v>300</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K8" t="str">
+        <v>いち</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1098,9 +1133,61 @@
         <v>いち</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>#7</v>
+      </c>
+      <c r="B18" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026/9/25 11:10:04</v>
+      </c>
+      <c r="D18" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E18">
+        <v>200</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>200</v>
+      </c>
+      <c r="H18" t="str">
+        <v>いち</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>#7</v>
+      </c>
+      <c r="B19" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026/9/25 11:10:04</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E19">
+        <v>200</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>200</v>
+      </c>
+      <c r="H19" t="str">
+        <v>いち</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -534,7 +534,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K4" t="str">
         <v>いちiPad</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -569,7 +569,7 @@
         <v>400</v>
       </c>
       <c r="J5" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K5" t="str">
         <v>いちiPad</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -604,7 +604,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K6" t="str">
         <v>いちiPad</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -639,7 +639,7 @@
         <v>200</v>
       </c>
       <c r="J7" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K7" t="str">
         <v>いち</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -674,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K8" t="str">
         <v>いち</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -680,16 +680,51 @@
         <v>いち</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>#8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2026/9/26 9:41:46</v>
+      </c>
+      <c r="D9" t="str">
+        <v>モンブラン×1, Hotココア×2</v>
+      </c>
+      <c r="E9">
+        <v>600</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>500</v>
+      </c>
+      <c r="H9">
+        <v>1000</v>
+      </c>
+      <c r="I9">
+        <v>500</v>
+      </c>
+      <c r="J9" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K9" t="str">
+        <v>reiPC</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1185,9 +1220,61 @@
         <v>いち</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>#8</v>
+      </c>
+      <c r="B20" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026/9/26 9:41:46</v>
+      </c>
+      <c r="D20" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E20">
+        <v>200</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>200</v>
+      </c>
+      <c r="H20" t="str">
+        <v>reiPC</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>#8</v>
+      </c>
+      <c r="B21" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026/9/26 9:41:46</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Hotココア</v>
+      </c>
+      <c r="E21">
+        <v>200</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>400</v>
+      </c>
+      <c r="H21" t="str">
+        <v>reiPC</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -709,7 +709,7 @@
         <v>500</v>
       </c>
       <c r="J9" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K9" t="str">
         <v>reiPC</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -715,16 +715,51 @@
         <v>reiPC</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>#9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>席 12</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2026/9/26 9:46:55</v>
+      </c>
+      <c r="D10" t="str">
+        <v>カラメルカスタード×1, Hotコーヒー×1</v>
+      </c>
+      <c r="E10">
+        <v>400</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10">
+        <v>300</v>
+      </c>
+      <c r="H10">
+        <v>500</v>
+      </c>
+      <c r="I10">
+        <v>200</v>
+      </c>
+      <c r="J10" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K10" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1272,9 +1307,61 @@
         <v>reiPC</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>#9</v>
+      </c>
+      <c r="B22" t="str">
+        <v>席 12</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026/9/26 9:46:55</v>
+      </c>
+      <c r="D22" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E22">
+        <v>200</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>200</v>
+      </c>
+      <c r="H22" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>#9</v>
+      </c>
+      <c r="B23" t="str">
+        <v>席 12</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026/9/26 9:46:55</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E23">
+        <v>200</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>200</v>
+      </c>
+      <c r="H23" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -744,7 +744,7 @@
         <v>200</v>
       </c>
       <c r="J10" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K10" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -750,16 +750,121 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>#10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026/9/26 9:52:40</v>
+      </c>
+      <c r="D11" t="str">
+        <v>チョコケーキ×2, プリンアラモード×1, Iceココア×2, カフェオレ(Hot)×1</v>
+      </c>
+      <c r="E11">
+        <v>1200</v>
+      </c>
+      <c r="F11">
+        <v>300</v>
+      </c>
+      <c r="G11">
+        <v>900</v>
+      </c>
+      <c r="H11">
+        <v>1000</v>
+      </c>
+      <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K11" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>#11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026/9/26 9:55:06</v>
+      </c>
+      <c r="D12" t="str">
+        <v>カラメルカスタード×1, Iceココア×1</v>
+      </c>
+      <c r="E12">
+        <v>400</v>
+      </c>
+      <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="G12">
+        <v>300</v>
+      </c>
+      <c r="H12">
+        <v>300</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K12" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>#12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2026/9/26 9:57:57</v>
+      </c>
+      <c r="D13" t="str">
+        <v>メロンクリームソーダ×1</v>
+      </c>
+      <c r="E13">
+        <v>200</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>200</v>
+      </c>
+      <c r="H13">
+        <v>200</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K13" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1359,9 +1464,191 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>#10</v>
+      </c>
+      <c r="B24" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2026/9/26 9:52:40</v>
+      </c>
+      <c r="D24" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E24">
+        <v>200</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>400</v>
+      </c>
+      <c r="H24" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>#10</v>
+      </c>
+      <c r="B25" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2026/9/26 9:52:40</v>
+      </c>
+      <c r="D25" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E25">
+        <v>200</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>200</v>
+      </c>
+      <c r="H25" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>#10</v>
+      </c>
+      <c r="B26" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2026/9/26 9:52:40</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E26">
+        <v>200</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>400</v>
+      </c>
+      <c r="H26" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>#10</v>
+      </c>
+      <c r="B27" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2026/9/26 9:52:40</v>
+      </c>
+      <c r="D27" t="str">
+        <v>カフェオレ(Hot)</v>
+      </c>
+      <c r="E27">
+        <v>200</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>200</v>
+      </c>
+      <c r="H27" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>#11</v>
+      </c>
+      <c r="B28" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C28" t="str">
+        <v>2026/9/26 9:55:06</v>
+      </c>
+      <c r="D28" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E28">
+        <v>200</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>200</v>
+      </c>
+      <c r="H28" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>#11</v>
+      </c>
+      <c r="B29" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C29" t="str">
+        <v>2026/9/26 9:55:06</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E29">
+        <v>200</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>200</v>
+      </c>
+      <c r="H29" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>#12</v>
+      </c>
+      <c r="B30" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C30" t="str">
+        <v>2026/9/26 9:57:57</v>
+      </c>
+      <c r="D30" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E30">
+        <v>200</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>200</v>
+      </c>
+      <c r="H30" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H30"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -779,7 +779,7 @@
         <v>100</v>
       </c>
       <c r="J11" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K11" t="str">
         <v>iti</v>
@@ -814,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K12" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K13" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -855,16 +855,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>#13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026/9/26 10:02:32</v>
+      </c>
+      <c r="D14" t="str">
+        <v>クリームチーズタルト×2, チョコケーキ×2, オレンジジュース×2</v>
+      </c>
+      <c r="E14">
+        <v>1200</v>
+      </c>
+      <c r="F14">
+        <v>200</v>
+      </c>
+      <c r="G14">
+        <v>1000</v>
+      </c>
+      <c r="H14">
+        <v>1000</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K14" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1646,9 +1681,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>#13</v>
+      </c>
+      <c r="B31" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C31" t="str">
+        <v>2026/9/26 10:02:32</v>
+      </c>
+      <c r="D31" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E31">
+        <v>200</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>400</v>
+      </c>
+      <c r="H31" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>#13</v>
+      </c>
+      <c r="B32" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C32" t="str">
+        <v>2026/9/26 10:02:32</v>
+      </c>
+      <c r="D32" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E32">
+        <v>200</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32">
+        <v>400</v>
+      </c>
+      <c r="H32" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>#13</v>
+      </c>
+      <c r="B33" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C33" t="str">
+        <v>2026/9/26 10:02:32</v>
+      </c>
+      <c r="D33" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E33">
+        <v>200</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>400</v>
+      </c>
+      <c r="H33" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H33"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -884,22 +884,57 @@
         <v>0</v>
       </c>
       <c r="J14" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K14" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>#14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026/9/26 10:05:56</v>
+      </c>
+      <c r="D15" t="str">
+        <v>モンブラン×1, クリームチーズタルト×1, Hotコーヒー×1, Ice紅茶×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E15">
+        <v>1000</v>
+      </c>
+      <c r="F15">
+        <v>200</v>
+      </c>
+      <c r="G15">
+        <v>800</v>
+      </c>
+      <c r="H15">
+        <v>1000</v>
+      </c>
+      <c r="I15">
+        <v>200</v>
+      </c>
+      <c r="J15" t="str">
         <v>提供待ち</v>
       </c>
-      <c r="K14" t="str">
+      <c r="K15" t="str">
         <v>iti</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1759,9 +1794,139 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>#14</v>
+      </c>
+      <c r="B34" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C34" t="str">
+        <v>2026/9/26 10:05:56</v>
+      </c>
+      <c r="D34" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E34">
+        <v>200</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>200</v>
+      </c>
+      <c r="H34" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>#14</v>
+      </c>
+      <c r="B35" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C35" t="str">
+        <v>2026/9/26 10:05:56</v>
+      </c>
+      <c r="D35" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E35">
+        <v>200</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>200</v>
+      </c>
+      <c r="H35" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>#14</v>
+      </c>
+      <c r="B36" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C36" t="str">
+        <v>2026/9/26 10:05:56</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E36">
+        <v>200</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>200</v>
+      </c>
+      <c r="H36" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>#14</v>
+      </c>
+      <c r="B37" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C37" t="str">
+        <v>2026/9/26 10:05:56</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E37">
+        <v>200</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>200</v>
+      </c>
+      <c r="H37" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>#14</v>
+      </c>
+      <c r="B38" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C38" t="str">
+        <v>2026/9/26 10:05:56</v>
+      </c>
+      <c r="D38" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E38">
+        <v>200</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>200</v>
+      </c>
+      <c r="H38" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H38"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -925,16 +925,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>#15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026/9/26 10:09:38</v>
+      </c>
+      <c r="D16" t="str">
+        <v>カラメルカスタード×1, チョコケーキ×1, 午後の紅茶 ミルクティー×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E16">
+        <v>800</v>
+      </c>
+      <c r="F16">
+        <v>200</v>
+      </c>
+      <c r="G16">
+        <v>600</v>
+      </c>
+      <c r="H16">
+        <v>600</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K16" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1924,9 +1959,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>#15</v>
+      </c>
+      <c r="B39" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C39" t="str">
+        <v>2026/9/26 10:09:38</v>
+      </c>
+      <c r="D39" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E39">
+        <v>200</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>200</v>
+      </c>
+      <c r="H39" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>#15</v>
+      </c>
+      <c r="B40" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C40" t="str">
+        <v>2026/9/26 10:09:38</v>
+      </c>
+      <c r="D40" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E40">
+        <v>200</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>200</v>
+      </c>
+      <c r="H40" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>#15</v>
+      </c>
+      <c r="B41" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C41" t="str">
+        <v>2026/9/26 10:09:38</v>
+      </c>
+      <c r="D41" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E41">
+        <v>200</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>200</v>
+      </c>
+      <c r="H41" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>#15</v>
+      </c>
+      <c r="B42" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C42" t="str">
+        <v>2026/9/26 10:09:38</v>
+      </c>
+      <c r="D42" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E42">
+        <v>200</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>200</v>
+      </c>
+      <c r="H42" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H42"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -919,7 +919,7 @@
         <v>200</v>
       </c>
       <c r="J15" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K15" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -960,16 +960,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>#16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026/9/26 10:10:43</v>
+      </c>
+      <c r="D17" t="str">
+        <v>チョコケーキ×1, プリンアラモード×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E17">
+        <v>600</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17">
+        <v>500</v>
+      </c>
+      <c r="H17">
+        <v>1000</v>
+      </c>
+      <c r="I17">
+        <v>500</v>
+      </c>
+      <c r="J17" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K17" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2063,9 +2098,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>#16</v>
+      </c>
+      <c r="B43" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C43" t="str">
+        <v>2026/9/26 10:10:43</v>
+      </c>
+      <c r="D43" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E43">
+        <v>200</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>200</v>
+      </c>
+      <c r="H43" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>#16</v>
+      </c>
+      <c r="B44" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C44" t="str">
+        <v>2026/9/26 10:10:43</v>
+      </c>
+      <c r="D44" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E44">
+        <v>200</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>200</v>
+      </c>
+      <c r="H44" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>#16</v>
+      </c>
+      <c r="B45" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C45" t="str">
+        <v>2026/9/26 10:10:43</v>
+      </c>
+      <c r="D45" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E45">
+        <v>200</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>200</v>
+      </c>
+      <c r="H45" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -995,16 +995,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>#17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026/9/26 10:12:20</v>
+      </c>
+      <c r="D18" t="str">
+        <v>クリームチーズタルト×1, チョコケーキ×1, Iceコーヒー×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E18">
+        <v>800</v>
+      </c>
+      <c r="F18">
+        <v>200</v>
+      </c>
+      <c r="G18">
+        <v>600</v>
+      </c>
+      <c r="H18">
+        <v>5000</v>
+      </c>
+      <c r="I18">
+        <v>4400</v>
+      </c>
+      <c r="J18" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K18" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K18"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2176,9 +2211,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>#17</v>
+      </c>
+      <c r="B46" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C46" t="str">
+        <v>2026/9/26 10:12:20</v>
+      </c>
+      <c r="D46" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E46">
+        <v>200</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>200</v>
+      </c>
+      <c r="H46" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>#17</v>
+      </c>
+      <c r="B47" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C47" t="str">
+        <v>2026/9/26 10:12:20</v>
+      </c>
+      <c r="D47" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E47">
+        <v>200</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>200</v>
+      </c>
+      <c r="H47" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>#17</v>
+      </c>
+      <c r="B48" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C48" t="str">
+        <v>2026/9/26 10:12:20</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E48">
+        <v>200</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>200</v>
+      </c>
+      <c r="H48" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>#17</v>
+      </c>
+      <c r="B49" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C49" t="str">
+        <v>2026/9/26 10:12:20</v>
+      </c>
+      <c r="D49" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E49">
+        <v>200</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>200</v>
+      </c>
+      <c r="H49" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H49"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K16" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1030,16 +1030,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>#18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026/9/26 10:13:16</v>
+      </c>
+      <c r="D19" t="str">
+        <v>クリームチーズタルト×2, Iceコーヒー×1, Ice紅茶×1</v>
+      </c>
+      <c r="E19">
+        <v>800</v>
+      </c>
+      <c r="F19">
+        <v>200</v>
+      </c>
+      <c r="G19">
+        <v>600</v>
+      </c>
+      <c r="H19">
+        <v>600</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K19" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K19"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H52"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2315,9 +2350,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>#18</v>
+      </c>
+      <c r="B50" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C50" t="str">
+        <v>2026/9/26 10:13:16</v>
+      </c>
+      <c r="D50" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E50">
+        <v>200</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="G50">
+        <v>400</v>
+      </c>
+      <c r="H50" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>#18</v>
+      </c>
+      <c r="B51" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C51" t="str">
+        <v>2026/9/26 10:13:16</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E51">
+        <v>200</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>200</v>
+      </c>
+      <c r="H51" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>#18</v>
+      </c>
+      <c r="B52" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C52" t="str">
+        <v>2026/9/26 10:13:16</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E52">
+        <v>200</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>200</v>
+      </c>
+      <c r="H52" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H52"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1065,16 +1065,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>#19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026/9/26 10:14:04</v>
+      </c>
+      <c r="D20" t="str">
+        <v>クリームチーズタルト×1, チョコケーキ×1, Iceコーヒー×1, Ice紅茶×1</v>
+      </c>
+      <c r="E20">
+        <v>800</v>
+      </c>
+      <c r="F20">
+        <v>200</v>
+      </c>
+      <c r="G20">
+        <v>600</v>
+      </c>
+      <c r="H20">
+        <v>1000</v>
+      </c>
+      <c r="I20">
+        <v>400</v>
+      </c>
+      <c r="J20" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K20" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K20"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2428,9 +2463,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>#19</v>
+      </c>
+      <c r="B53" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C53" t="str">
+        <v>2026/9/26 10:14:04</v>
+      </c>
+      <c r="D53" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E53">
+        <v>200</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>200</v>
+      </c>
+      <c r="H53" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>#19</v>
+      </c>
+      <c r="B54" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C54" t="str">
+        <v>2026/9/26 10:14:04</v>
+      </c>
+      <c r="D54" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E54">
+        <v>200</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>200</v>
+      </c>
+      <c r="H54" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>#19</v>
+      </c>
+      <c r="B55" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C55" t="str">
+        <v>2026/9/26 10:14:04</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E55">
+        <v>200</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>200</v>
+      </c>
+      <c r="H55" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>#19</v>
+      </c>
+      <c r="B56" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C56" t="str">
+        <v>2026/9/26 10:14:04</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E56">
+        <v>200</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>200</v>
+      </c>
+      <c r="H56" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H56"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -989,7 +989,7 @@
         <v>500</v>
       </c>
       <c r="J17" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K17" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1024,7 +1024,7 @@
         <v>4400</v>
       </c>
       <c r="J18" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K18" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1100,16 +1100,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>#20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026/9/26 10:16:46</v>
+      </c>
+      <c r="D21" t="str">
+        <v>モンブラン×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E21">
+        <v>400</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="G21">
+        <v>300</v>
+      </c>
+      <c r="H21">
+        <v>500</v>
+      </c>
+      <c r="I21">
+        <v>200</v>
+      </c>
+      <c r="J21" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K21" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K21"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H58"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2567,9 +2602,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>#20</v>
+      </c>
+      <c r="B57" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C57" t="str">
+        <v>2026/9/26 10:16:46</v>
+      </c>
+      <c r="D57" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E57">
+        <v>200</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>200</v>
+      </c>
+      <c r="H57" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>#20</v>
+      </c>
+      <c r="B58" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C58" t="str">
+        <v>2026/9/26 10:16:46</v>
+      </c>
+      <c r="D58" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E58">
+        <v>200</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>200</v>
+      </c>
+      <c r="H58" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H58"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K19" t="str">
         <v>iti</v>
@@ -1135,16 +1135,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>#21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026/9/26 10:18:18</v>
+      </c>
+      <c r="D22" t="str">
+        <v>カラメルカスタード×1, モンブラン×1, プリンアラモード×1, Hotコーヒー×2, Iceコーヒー×1</v>
+      </c>
+      <c r="E22">
+        <v>1200</v>
+      </c>
+      <c r="F22">
+        <v>300</v>
+      </c>
+      <c r="G22">
+        <v>900</v>
+      </c>
+      <c r="H22">
+        <v>1000</v>
+      </c>
+      <c r="I22">
+        <v>100</v>
+      </c>
+      <c r="J22" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K22" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2654,9 +2689,139 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>#21</v>
+      </c>
+      <c r="B59" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C59" t="str">
+        <v>2026/9/26 10:18:18</v>
+      </c>
+      <c r="D59" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E59">
+        <v>200</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>200</v>
+      </c>
+      <c r="H59" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>#21</v>
+      </c>
+      <c r="B60" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C60" t="str">
+        <v>2026/9/26 10:18:18</v>
+      </c>
+      <c r="D60" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E60">
+        <v>200</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>200</v>
+      </c>
+      <c r="H60" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>#21</v>
+      </c>
+      <c r="B61" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C61" t="str">
+        <v>2026/9/26 10:18:18</v>
+      </c>
+      <c r="D61" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E61">
+        <v>200</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>200</v>
+      </c>
+      <c r="H61" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>#21</v>
+      </c>
+      <c r="B62" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C62" t="str">
+        <v>2026/9/26 10:18:18</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E62">
+        <v>200</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62">
+        <v>400</v>
+      </c>
+      <c r="H62" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>#21</v>
+      </c>
+      <c r="B63" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C63" t="str">
+        <v>2026/9/26 10:18:18</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E63">
+        <v>200</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <v>200</v>
+      </c>
+      <c r="H63" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H63"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1170,16 +1170,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>#22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026/9/26 10:19:40</v>
+      </c>
+      <c r="D23" t="str">
+        <v>カラメルカスタード×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E23">
+        <v>400</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23">
+        <v>300</v>
+      </c>
+      <c r="H23">
+        <v>1000</v>
+      </c>
+      <c r="I23">
+        <v>700</v>
+      </c>
+      <c r="J23" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K23" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H65"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2819,9 +2854,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>#22</v>
+      </c>
+      <c r="B64" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C64" t="str">
+        <v>2026/9/26 10:19:40</v>
+      </c>
+      <c r="D64" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E64">
+        <v>200</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>200</v>
+      </c>
+      <c r="H64" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>#22</v>
+      </c>
+      <c r="B65" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C65" t="str">
+        <v>2026/9/26 10:19:40</v>
+      </c>
+      <c r="D65" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E65">
+        <v>200</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>200</v>
+      </c>
+      <c r="H65" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H65"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1129,7 +1129,7 @@
         <v>200</v>
       </c>
       <c r="J21" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K21" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1205,16 +1205,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>#23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2026/9/26 10:20:58</v>
+      </c>
+      <c r="D24" t="str">
+        <v>モンブラン×2, クリームチーズタルト×1, Iceコーヒー×2, Ice紅茶×1</v>
+      </c>
+      <c r="E24">
+        <v>1200</v>
+      </c>
+      <c r="F24">
+        <v>300</v>
+      </c>
+      <c r="G24">
+        <v>900</v>
+      </c>
+      <c r="H24">
+        <v>1000</v>
+      </c>
+      <c r="I24">
+        <v>100</v>
+      </c>
+      <c r="J24" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K24" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K24"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H69"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2906,9 +2941,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>#23</v>
+      </c>
+      <c r="B66" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C66" t="str">
+        <v>2026/9/26 10:20:58</v>
+      </c>
+      <c r="D66" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E66">
+        <v>200</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66">
+        <v>400</v>
+      </c>
+      <c r="H66" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>#23</v>
+      </c>
+      <c r="B67" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C67" t="str">
+        <v>2026/9/26 10:20:58</v>
+      </c>
+      <c r="D67" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E67">
+        <v>200</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>200</v>
+      </c>
+      <c r="H67" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>#23</v>
+      </c>
+      <c r="B68" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C68" t="str">
+        <v>2026/9/26 10:20:58</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E68">
+        <v>200</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="G68">
+        <v>400</v>
+      </c>
+      <c r="H68" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>#23</v>
+      </c>
+      <c r="B69" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C69" t="str">
+        <v>2026/9/26 10:20:58</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E69">
+        <v>200</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>200</v>
+      </c>
+      <c r="H69" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1240,16 +1240,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>#24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2026/9/26 10:22:22</v>
+      </c>
+      <c r="D25" t="str">
+        <v>カラメルカスタード×1, Iceココア×1, カフェオレ(Hot)×1</v>
+      </c>
+      <c r="E25">
+        <v>600</v>
+      </c>
+      <c r="F25">
+        <v>400</v>
+      </c>
+      <c r="G25">
+        <v>200</v>
+      </c>
+      <c r="H25">
+        <v>600</v>
+      </c>
+      <c r="I25">
+        <v>400</v>
+      </c>
+      <c r="J25" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K25" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K25"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H72"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3045,9 +3080,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>#24</v>
+      </c>
+      <c r="B70" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C70" t="str">
+        <v>2026/9/26 10:22:22</v>
+      </c>
+      <c r="D70" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E70">
+        <v>200</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>200</v>
+      </c>
+      <c r="H70" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>#24</v>
+      </c>
+      <c r="B71" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C71" t="str">
+        <v>2026/9/26 10:22:22</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E71">
+        <v>200</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>200</v>
+      </c>
+      <c r="H71" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>#24</v>
+      </c>
+      <c r="B72" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C72" t="str">
+        <v>2026/9/26 10:22:22</v>
+      </c>
+      <c r="D72" t="str">
+        <v>カフェオレ(Hot)</v>
+      </c>
+      <c r="E72">
+        <v>200</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>200</v>
+      </c>
+      <c r="H72" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H72"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1275,16 +1275,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>#25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2026/9/26 10:24:25</v>
+      </c>
+      <c r="D26" t="str">
+        <v>モンブラン×1, チョコケーキ×1, Hotココア×2</v>
+      </c>
+      <c r="E26">
+        <v>800</v>
+      </c>
+      <c r="F26">
+        <v>200</v>
+      </c>
+      <c r="G26">
+        <v>600</v>
+      </c>
+      <c r="H26">
+        <v>600</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K26" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K26"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H75"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3158,9 +3193,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>#25</v>
+      </c>
+      <c r="B73" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C73" t="str">
+        <v>2026/9/26 10:24:25</v>
+      </c>
+      <c r="D73" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E73">
+        <v>200</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <v>200</v>
+      </c>
+      <c r="H73" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>#25</v>
+      </c>
+      <c r="B74" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C74" t="str">
+        <v>2026/9/26 10:24:25</v>
+      </c>
+      <c r="D74" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E74">
+        <v>200</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>200</v>
+      </c>
+      <c r="H74" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>#25</v>
+      </c>
+      <c r="B75" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C75" t="str">
+        <v>2026/9/26 10:24:25</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Hotココア</v>
+      </c>
+      <c r="E75">
+        <v>200</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+      <c r="G75">
+        <v>400</v>
+      </c>
+      <c r="H75" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H75"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1094,7 +1094,7 @@
         <v>400</v>
       </c>
       <c r="J20" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K20" t="str">
         <v>iti</v>
@@ -1164,7 +1164,7 @@
         <v>100</v>
       </c>
       <c r="J22" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K22" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1199,7 +1199,7 @@
         <v>700</v>
       </c>
       <c r="J23" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K23" t="str">
         <v>iti</v>
@@ -1234,7 +1234,7 @@
         <v>100</v>
       </c>
       <c r="J24" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K24" t="str">
         <v>iti</v>
@@ -1310,16 +1310,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>#26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>席 11</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2026/9/26 10:27:08</v>
+      </c>
+      <c r="D27" t="str">
+        <v>カラメルカスタード×1, モンブラン×2, Ice紅茶×1, Iceココア×1</v>
+      </c>
+      <c r="E27">
+        <v>1000</v>
+      </c>
+      <c r="F27">
+        <v>200</v>
+      </c>
+      <c r="G27">
+        <v>800</v>
+      </c>
+      <c r="H27">
+        <v>1500</v>
+      </c>
+      <c r="I27">
+        <v>700</v>
+      </c>
+      <c r="J27" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K27" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K27"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H79"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3271,9 +3306,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>#26</v>
+      </c>
+      <c r="B76" t="str">
+        <v>席 11</v>
+      </c>
+      <c r="C76" t="str">
+        <v>2026/9/26 10:27:08</v>
+      </c>
+      <c r="D76" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E76">
+        <v>200</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>200</v>
+      </c>
+      <c r="H76" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>#26</v>
+      </c>
+      <c r="B77" t="str">
+        <v>席 11</v>
+      </c>
+      <c r="C77" t="str">
+        <v>2026/9/26 10:27:08</v>
+      </c>
+      <c r="D77" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E77">
+        <v>200</v>
+      </c>
+      <c r="F77">
+        <v>2</v>
+      </c>
+      <c r="G77">
+        <v>400</v>
+      </c>
+      <c r="H77" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>#26</v>
+      </c>
+      <c r="B78" t="str">
+        <v>席 11</v>
+      </c>
+      <c r="C78" t="str">
+        <v>2026/9/26 10:27:08</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E78">
+        <v>200</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <v>200</v>
+      </c>
+      <c r="H78" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>#26</v>
+      </c>
+      <c r="B79" t="str">
+        <v>席 11</v>
+      </c>
+      <c r="C79" t="str">
+        <v>2026/9/26 10:27:08</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E79">
+        <v>200</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>200</v>
+      </c>
+      <c r="H79" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H75"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1269,7 +1269,7 @@
         <v>400</v>
       </c>
       <c r="J25" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K25" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1345,16 +1345,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>#27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C28" t="str">
+        <v>2026/9/26 10:29:22</v>
+      </c>
+      <c r="D28" t="str">
+        <v>モンブラン×1, クリームチーズタルト×1, Hotコーヒー×2</v>
+      </c>
+      <c r="E28">
+        <v>800</v>
+      </c>
+      <c r="F28">
+        <v>200</v>
+      </c>
+      <c r="G28">
+        <v>600</v>
+      </c>
+      <c r="H28">
+        <v>1000</v>
+      </c>
+      <c r="I28">
+        <v>400</v>
+      </c>
+      <c r="J28" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K28" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K28"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3410,9 +3445,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>#27</v>
+      </c>
+      <c r="B80" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C80" t="str">
+        <v>2026/9/26 10:29:22</v>
+      </c>
+      <c r="D80" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E80">
+        <v>200</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80">
+        <v>200</v>
+      </c>
+      <c r="H80" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>#27</v>
+      </c>
+      <c r="B81" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C81" t="str">
+        <v>2026/9/26 10:29:22</v>
+      </c>
+      <c r="D81" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E81">
+        <v>200</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81">
+        <v>200</v>
+      </c>
+      <c r="H81" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>#27</v>
+      </c>
+      <c r="B82" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C82" t="str">
+        <v>2026/9/26 10:29:22</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E82">
+        <v>200</v>
+      </c>
+      <c r="F82">
+        <v>2</v>
+      </c>
+      <c r="G82">
+        <v>400</v>
+      </c>
+      <c r="H82" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H82"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1339,7 +1339,7 @@
         <v>700</v>
       </c>
       <c r="J27" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K27" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K26" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1380,16 +1380,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>#28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C29" t="str">
+        <v>2026/9/26 10:32:25</v>
+      </c>
+      <c r="D29" t="str">
+        <v>モンブラン×2, クリームチーズタルト×1, Iceコーヒー×1, Ice紅茶×2</v>
+      </c>
+      <c r="E29">
+        <v>1200</v>
+      </c>
+      <c r="F29">
+        <v>300</v>
+      </c>
+      <c r="G29">
+        <v>900</v>
+      </c>
+      <c r="H29">
+        <v>900</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K29" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K29"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H86"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3523,9 +3558,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>#28</v>
+      </c>
+      <c r="B83" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C83" t="str">
+        <v>2026/9/26 10:32:25</v>
+      </c>
+      <c r="D83" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E83">
+        <v>200</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83">
+        <v>400</v>
+      </c>
+      <c r="H83" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>#28</v>
+      </c>
+      <c r="B84" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C84" t="str">
+        <v>2026/9/26 10:32:25</v>
+      </c>
+      <c r="D84" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E84">
+        <v>200</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84">
+        <v>200</v>
+      </c>
+      <c r="H84" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>#28</v>
+      </c>
+      <c r="B85" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C85" t="str">
+        <v>2026/9/26 10:32:25</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E85">
+        <v>200</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>200</v>
+      </c>
+      <c r="H85" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>#28</v>
+      </c>
+      <c r="B86" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C86" t="str">
+        <v>2026/9/26 10:32:25</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E86">
+        <v>200</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="G86">
+        <v>400</v>
+      </c>
+      <c r="H86" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H86"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1374,7 +1374,7 @@
         <v>400</v>
       </c>
       <c r="J28" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K28" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1415,16 +1415,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>#29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C30" t="str">
+        <v>2026/9/26 10:33:37</v>
+      </c>
+      <c r="D30" t="str">
+        <v>モンブラン×1, クリームチーズタルト×1, Iceココア×2</v>
+      </c>
+      <c r="E30">
+        <v>800</v>
+      </c>
+      <c r="F30">
+        <v>200</v>
+      </c>
+      <c r="G30">
+        <v>600</v>
+      </c>
+      <c r="H30">
+        <v>600</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K30" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H89"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3662,9 +3697,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>#29</v>
+      </c>
+      <c r="B87" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C87" t="str">
+        <v>2026/9/26 10:33:37</v>
+      </c>
+      <c r="D87" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E87">
+        <v>200</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>200</v>
+      </c>
+      <c r="H87" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>#29</v>
+      </c>
+      <c r="B88" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C88" t="str">
+        <v>2026/9/26 10:33:37</v>
+      </c>
+      <c r="D88" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E88">
+        <v>200</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>200</v>
+      </c>
+      <c r="H88" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>#29</v>
+      </c>
+      <c r="B89" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C89" t="str">
+        <v>2026/9/26 10:33:37</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E89">
+        <v>200</v>
+      </c>
+      <c r="F89">
+        <v>2</v>
+      </c>
+      <c r="G89">
+        <v>400</v>
+      </c>
+      <c r="H89" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H86"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H89"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K29" t="str">
         <v>iti</v>
@@ -1450,16 +1450,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>#30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C31" t="str">
+        <v>2026/9/26 10:34:35</v>
+      </c>
+      <c r="D31" t="str">
+        <v>チョコケーキ×2, 午後の紅茶 ミルクティー×2</v>
+      </c>
+      <c r="E31">
+        <v>800</v>
+      </c>
+      <c r="F31">
+        <v>200</v>
+      </c>
+      <c r="G31">
+        <v>600</v>
+      </c>
+      <c r="H31">
+        <v>800</v>
+      </c>
+      <c r="I31">
+        <v>200</v>
+      </c>
+      <c r="J31" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K31" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K31"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3775,9 +3810,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>#30</v>
+      </c>
+      <c r="B90" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C90" t="str">
+        <v>2026/9/26 10:34:35</v>
+      </c>
+      <c r="D90" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E90">
+        <v>200</v>
+      </c>
+      <c r="F90">
+        <v>2</v>
+      </c>
+      <c r="G90">
+        <v>400</v>
+      </c>
+      <c r="H90" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>#30</v>
+      </c>
+      <c r="B91" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C91" t="str">
+        <v>2026/9/26 10:34:35</v>
+      </c>
+      <c r="D91" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E91">
+        <v>200</v>
+      </c>
+      <c r="F91">
+        <v>2</v>
+      </c>
+      <c r="G91">
+        <v>400</v>
+      </c>
+      <c r="H91" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H89"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H91"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1485,16 +1485,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>#31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C32" t="str">
+        <v>2026/9/26 10:35:46</v>
+      </c>
+      <c r="D32" t="str">
+        <v>チョコケーキ×1, 午後の紅茶 ミルクティー×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E32">
+        <v>600</v>
+      </c>
+      <c r="F32">
+        <v>400</v>
+      </c>
+      <c r="G32">
+        <v>200</v>
+      </c>
+      <c r="H32">
+        <v>10000</v>
+      </c>
+      <c r="I32">
+        <v>9800</v>
+      </c>
+      <c r="J32" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K32" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K32"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3862,9 +3897,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>#31</v>
+      </c>
+      <c r="B92" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C92" t="str">
+        <v>2026/9/26 10:35:46</v>
+      </c>
+      <c r="D92" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E92">
+        <v>200</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92">
+        <v>200</v>
+      </c>
+      <c r="H92" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>#31</v>
+      </c>
+      <c r="B93" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C93" t="str">
+        <v>2026/9/26 10:35:46</v>
+      </c>
+      <c r="D93" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E93">
+        <v>200</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>200</v>
+      </c>
+      <c r="H93" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>#31</v>
+      </c>
+      <c r="B94" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C94" t="str">
+        <v>2026/9/26 10:35:46</v>
+      </c>
+      <c r="D94" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E94">
+        <v>200</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94">
+        <v>200</v>
+      </c>
+      <c r="H94" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H94"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K30" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1479,7 +1479,7 @@
         <v>200</v>
       </c>
       <c r="J31" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K31" t="str">
         <v>iti</v>
@@ -1520,16 +1520,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>#32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C33" t="str">
+        <v>2026/9/26 10:36:39</v>
+      </c>
+      <c r="D33" t="str">
+        <v>モンブラン×1, チョコケーキ×1, Iceコーヒー×2</v>
+      </c>
+      <c r="E33">
+        <v>800</v>
+      </c>
+      <c r="F33">
+        <v>200</v>
+      </c>
+      <c r="G33">
+        <v>600</v>
+      </c>
+      <c r="H33">
+        <v>1100</v>
+      </c>
+      <c r="I33">
+        <v>500</v>
+      </c>
+      <c r="J33" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K33" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K33"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3975,9 +4010,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>#32</v>
+      </c>
+      <c r="B95" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C95" t="str">
+        <v>2026/9/26 10:36:39</v>
+      </c>
+      <c r="D95" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E95">
+        <v>200</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <v>200</v>
+      </c>
+      <c r="H95" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>#32</v>
+      </c>
+      <c r="B96" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C96" t="str">
+        <v>2026/9/26 10:36:39</v>
+      </c>
+      <c r="D96" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E96">
+        <v>200</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96">
+        <v>200</v>
+      </c>
+      <c r="H96" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>#32</v>
+      </c>
+      <c r="B97" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C97" t="str">
+        <v>2026/9/26 10:36:39</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E97">
+        <v>200</v>
+      </c>
+      <c r="F97">
+        <v>2</v>
+      </c>
+      <c r="G97">
+        <v>400</v>
+      </c>
+      <c r="H97" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H97"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1549,7 +1549,7 @@
         <v>500</v>
       </c>
       <c r="J33" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K33" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1514,7 +1514,7 @@
         <v>9800</v>
       </c>
       <c r="J32" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K32" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1555,16 +1555,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>#33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C34" t="str">
+        <v>2026/9/26 10:40:14</v>
+      </c>
+      <c r="D34" t="str">
+        <v>カラメルカスタード×1, チョコケーキ×1, Iceコーヒー×1, Hot紅茶×1</v>
+      </c>
+      <c r="E34">
+        <v>800</v>
+      </c>
+      <c r="F34">
+        <v>200</v>
+      </c>
+      <c r="G34">
+        <v>600</v>
+      </c>
+      <c r="H34">
+        <v>600</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K34" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K34"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4088,9 +4123,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>#33</v>
+      </c>
+      <c r="B98" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C98" t="str">
+        <v>2026/9/26 10:40:14</v>
+      </c>
+      <c r="D98" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E98">
+        <v>200</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
+        <v>200</v>
+      </c>
+      <c r="H98" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>#33</v>
+      </c>
+      <c r="B99" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C99" t="str">
+        <v>2026/9/26 10:40:14</v>
+      </c>
+      <c r="D99" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E99">
+        <v>200</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>200</v>
+      </c>
+      <c r="H99" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>#33</v>
+      </c>
+      <c r="B100" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C100" t="str">
+        <v>2026/9/26 10:40:14</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E100">
+        <v>200</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100">
+        <v>200</v>
+      </c>
+      <c r="H100" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>#33</v>
+      </c>
+      <c r="B101" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C101" t="str">
+        <v>2026/9/26 10:40:14</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Hot紅茶</v>
+      </c>
+      <c r="E101">
+        <v>200</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>200</v>
+      </c>
+      <c r="H101" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1590,16 +1590,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>#34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C35" t="str">
+        <v>2026/9/26 10:44:15</v>
+      </c>
+      <c r="D35" t="str">
+        <v>クリームチーズタルト×2, Iceコーヒー×1</v>
+      </c>
+      <c r="E35">
+        <v>600</v>
+      </c>
+      <c r="F35">
+        <v>100</v>
+      </c>
+      <c r="G35">
+        <v>500</v>
+      </c>
+      <c r="H35">
+        <v>5000</v>
+      </c>
+      <c r="I35">
+        <v>4500</v>
+      </c>
+      <c r="J35" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K35" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K35"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4227,9 +4262,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>#34</v>
+      </c>
+      <c r="B102" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C102" t="str">
+        <v>2026/9/26 10:44:15</v>
+      </c>
+      <c r="D102" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E102">
+        <v>200</v>
+      </c>
+      <c r="F102">
+        <v>2</v>
+      </c>
+      <c r="G102">
+        <v>400</v>
+      </c>
+      <c r="H102" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>#34</v>
+      </c>
+      <c r="B103" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C103" t="str">
+        <v>2026/9/26 10:44:15</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E103">
+        <v>200</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="G103">
+        <v>200</v>
+      </c>
+      <c r="H103" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H103"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1584,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K34" t="str">
         <v>iti</v>
@@ -1625,16 +1625,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>#35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C36" t="str">
+        <v>2026/9/26 10:44:48</v>
+      </c>
+      <c r="D36" t="str">
+        <v>チョコケーキ×1, カフェオレ(Hot)×1</v>
+      </c>
+      <c r="E36">
+        <v>400</v>
+      </c>
+      <c r="F36">
+        <v>100</v>
+      </c>
+      <c r="G36">
+        <v>300</v>
+      </c>
+      <c r="H36">
+        <v>300</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K36" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K36"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4314,9 +4349,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>#35</v>
+      </c>
+      <c r="B104" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C104" t="str">
+        <v>2026/9/26 10:44:48</v>
+      </c>
+      <c r="D104" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E104">
+        <v>200</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="G104">
+        <v>200</v>
+      </c>
+      <c r="H104" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>#35</v>
+      </c>
+      <c r="B105" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C105" t="str">
+        <v>2026/9/26 10:44:48</v>
+      </c>
+      <c r="D105" t="str">
+        <v>カフェオレ(Hot)</v>
+      </c>
+      <c r="E105">
+        <v>200</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="G105">
+        <v>200</v>
+      </c>
+      <c r="H105" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H105"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1619,7 +1619,7 @@
         <v>4500</v>
       </c>
       <c r="J35" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K35" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1660,16 +1660,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>#36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C37" t="str">
+        <v>2026/9/26 10:45:35</v>
+      </c>
+      <c r="D37" t="str">
+        <v>オレンジジュース×1</v>
+      </c>
+      <c r="E37">
+        <v>200</v>
+      </c>
+      <c r="F37">
+        <v>200</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>300</v>
+      </c>
+      <c r="I37">
+        <v>300</v>
+      </c>
+      <c r="J37" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K37" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K37"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H106"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4401,9 +4436,35 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>#36</v>
+      </c>
+      <c r="B106" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C106" t="str">
+        <v>2026/9/26 10:45:35</v>
+      </c>
+      <c r="D106" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E106">
+        <v>200</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="G106">
+        <v>200</v>
+      </c>
+      <c r="H106" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H106"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K36" t="str">
         <v>iti</v>
@@ -1689,7 +1689,7 @@
         <v>300</v>
       </c>
       <c r="J37" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K37" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1695,16 +1695,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>#37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C38" t="str">
+        <v>2026/9/26 10:49:53</v>
+      </c>
+      <c r="D38" t="str">
+        <v>モンブラン×1, カフェオレ(Hot)×1</v>
+      </c>
+      <c r="E38">
+        <v>400</v>
+      </c>
+      <c r="F38">
+        <v>100</v>
+      </c>
+      <c r="G38">
+        <v>300</v>
+      </c>
+      <c r="H38">
+        <v>500</v>
+      </c>
+      <c r="I38">
+        <v>200</v>
+      </c>
+      <c r="J38" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K38" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K38"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H108"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4462,9 +4497,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>#37</v>
+      </c>
+      <c r="B107" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C107" t="str">
+        <v>2026/9/26 10:49:53</v>
+      </c>
+      <c r="D107" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E107">
+        <v>200</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107">
+        <v>200</v>
+      </c>
+      <c r="H107" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>#37</v>
+      </c>
+      <c r="B108" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C108" t="str">
+        <v>2026/9/26 10:49:53</v>
+      </c>
+      <c r="D108" t="str">
+        <v>カフェオレ(Hot)</v>
+      </c>
+      <c r="E108">
+        <v>200</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108">
+        <v>200</v>
+      </c>
+      <c r="H108" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H106"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1724,7 +1724,7 @@
         <v>200</v>
       </c>
       <c r="J38" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K38" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K40"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1730,16 +1730,86 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>#38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C39" t="str">
+        <v>2026/9/26 10:52:50</v>
+      </c>
+      <c r="D39" t="str">
+        <v>モンブラン×1, チョコケーキ×1, Iceココア×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E39">
+        <v>800</v>
+      </c>
+      <c r="F39">
+        <v>200</v>
+      </c>
+      <c r="G39">
+        <v>600</v>
+      </c>
+      <c r="H39">
+        <v>600</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K39" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>#39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C40" t="str">
+        <v>2026/9/26 10:53:26</v>
+      </c>
+      <c r="D40" t="str">
+        <v>モンブラン×1, クリームチーズタルト×1, Iceコーヒー×1, Ice紅茶×1</v>
+      </c>
+      <c r="E40">
+        <v>800</v>
+      </c>
+      <c r="F40">
+        <v>200</v>
+      </c>
+      <c r="G40">
+        <v>600</v>
+      </c>
+      <c r="H40">
+        <v>1000</v>
+      </c>
+      <c r="I40">
+        <v>400</v>
+      </c>
+      <c r="J40" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K40" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K40"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H116"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4549,9 +4619,217 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>#38</v>
+      </c>
+      <c r="B109" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C109" t="str">
+        <v>2026/9/26 10:52:50</v>
+      </c>
+      <c r="D109" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E109">
+        <v>200</v>
+      </c>
+      <c r="F109">
+        <v>1</v>
+      </c>
+      <c r="G109">
+        <v>200</v>
+      </c>
+      <c r="H109" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>#38</v>
+      </c>
+      <c r="B110" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C110" t="str">
+        <v>2026/9/26 10:52:50</v>
+      </c>
+      <c r="D110" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E110">
+        <v>200</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="G110">
+        <v>200</v>
+      </c>
+      <c r="H110" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>#38</v>
+      </c>
+      <c r="B111" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C111" t="str">
+        <v>2026/9/26 10:52:50</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E111">
+        <v>200</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="G111">
+        <v>200</v>
+      </c>
+      <c r="H111" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>#38</v>
+      </c>
+      <c r="B112" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C112" t="str">
+        <v>2026/9/26 10:52:50</v>
+      </c>
+      <c r="D112" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E112">
+        <v>200</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112">
+        <v>200</v>
+      </c>
+      <c r="H112" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>#39</v>
+      </c>
+      <c r="B113" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C113" t="str">
+        <v>2026/9/26 10:53:26</v>
+      </c>
+      <c r="D113" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E113">
+        <v>200</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="G113">
+        <v>200</v>
+      </c>
+      <c r="H113" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>#39</v>
+      </c>
+      <c r="B114" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C114" t="str">
+        <v>2026/9/26 10:53:26</v>
+      </c>
+      <c r="D114" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E114">
+        <v>200</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="G114">
+        <v>200</v>
+      </c>
+      <c r="H114" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>#39</v>
+      </c>
+      <c r="B115" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C115" t="str">
+        <v>2026/9/26 10:53:26</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E115">
+        <v>200</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115">
+        <v>200</v>
+      </c>
+      <c r="H115" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>#39</v>
+      </c>
+      <c r="B116" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C116" t="str">
+        <v>2026/9/26 10:53:26</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E116">
+        <v>200</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116">
+        <v>200</v>
+      </c>
+      <c r="H116" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H116"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1794,7 +1794,7 @@
         <v>400</v>
       </c>
       <c r="J40" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K40" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K39" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1800,16 +1800,86 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>#40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C41" t="str">
+        <v>2026/9/26 10:59:06</v>
+      </c>
+      <c r="D41" t="str">
+        <v>クリームチーズタルト×2, 午後の紅茶 ミルクティー×1, メロンクリームソーダ×2</v>
+      </c>
+      <c r="E41">
+        <v>1000</v>
+      </c>
+      <c r="F41">
+        <v>200</v>
+      </c>
+      <c r="G41">
+        <v>800</v>
+      </c>
+      <c r="H41">
+        <v>1000</v>
+      </c>
+      <c r="I41">
+        <v>200</v>
+      </c>
+      <c r="J41" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K41" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>#41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C42" t="str">
+        <v>2026/9/26 11:01:20</v>
+      </c>
+      <c r="D42" t="str">
+        <v>モンブラン×2, チョコケーキ×2, Iceコーヒー×1, Hot紅茶×1, Iceココア×1</v>
+      </c>
+      <c r="E42">
+        <v>1400</v>
+      </c>
+      <c r="F42">
+        <v>300</v>
+      </c>
+      <c r="G42">
+        <v>1100</v>
+      </c>
+      <c r="H42">
+        <v>1100</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K42" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K42"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H124"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4827,9 +4897,217 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>#40</v>
+      </c>
+      <c r="B117" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C117" t="str">
+        <v>2026/9/26 10:59:06</v>
+      </c>
+      <c r="D117" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E117">
+        <v>200</v>
+      </c>
+      <c r="F117">
+        <v>2</v>
+      </c>
+      <c r="G117">
+        <v>400</v>
+      </c>
+      <c r="H117" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>#40</v>
+      </c>
+      <c r="B118" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C118" t="str">
+        <v>2026/9/26 10:59:06</v>
+      </c>
+      <c r="D118" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E118">
+        <v>200</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118">
+        <v>200</v>
+      </c>
+      <c r="H118" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>#40</v>
+      </c>
+      <c r="B119" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C119" t="str">
+        <v>2026/9/26 10:59:06</v>
+      </c>
+      <c r="D119" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E119">
+        <v>200</v>
+      </c>
+      <c r="F119">
+        <v>2</v>
+      </c>
+      <c r="G119">
+        <v>400</v>
+      </c>
+      <c r="H119" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>#41</v>
+      </c>
+      <c r="B120" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C120" t="str">
+        <v>2026/9/26 11:01:20</v>
+      </c>
+      <c r="D120" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E120">
+        <v>200</v>
+      </c>
+      <c r="F120">
+        <v>2</v>
+      </c>
+      <c r="G120">
+        <v>400</v>
+      </c>
+      <c r="H120" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>#41</v>
+      </c>
+      <c r="B121" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C121" t="str">
+        <v>2026/9/26 11:01:20</v>
+      </c>
+      <c r="D121" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E121">
+        <v>200</v>
+      </c>
+      <c r="F121">
+        <v>2</v>
+      </c>
+      <c r="G121">
+        <v>400</v>
+      </c>
+      <c r="H121" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>#41</v>
+      </c>
+      <c r="B122" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C122" t="str">
+        <v>2026/9/26 11:01:20</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E122">
+        <v>200</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122">
+        <v>200</v>
+      </c>
+      <c r="H122" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>#41</v>
+      </c>
+      <c r="B123" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C123" t="str">
+        <v>2026/9/26 11:01:20</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Hot紅茶</v>
+      </c>
+      <c r="E123">
+        <v>200</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123">
+        <v>200</v>
+      </c>
+      <c r="H123" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>#41</v>
+      </c>
+      <c r="B124" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C124" t="str">
+        <v>2026/9/26 11:01:20</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E124">
+        <v>200</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124">
+        <v>200</v>
+      </c>
+      <c r="H124" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H116"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H124"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1870,16 +1870,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>#42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>席 13</v>
+      </c>
+      <c r="C43" t="str">
+        <v>2026/9/26 11:03:12</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Ice紅茶×1</v>
+      </c>
+      <c r="E43">
+        <v>200</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>200</v>
+      </c>
+      <c r="H43">
+        <v>200</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K43" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K43"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H125"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5105,9 +5140,35 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>#42</v>
+      </c>
+      <c r="B125" t="str">
+        <v>席 13</v>
+      </c>
+      <c r="C125" t="str">
+        <v>2026/9/26 11:03:12</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E125">
+        <v>200</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125">
+        <v>200</v>
+      </c>
+      <c r="H125" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H124"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H125"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1864,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K42" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1905,16 +1905,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>#43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C44" t="str">
+        <v>2026/9/26 11:08:06</v>
+      </c>
+      <c r="D44" t="str">
+        <v>クリームチーズタルト×3, プリンアラモード×1, Hotコーヒー×1, Iceコーヒー×2, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E44">
+        <v>1600</v>
+      </c>
+      <c r="F44">
+        <v>400</v>
+      </c>
+      <c r="G44">
+        <v>1200</v>
+      </c>
+      <c r="H44">
+        <v>1200</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K44" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K44"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H130"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5166,9 +5201,139 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>#43</v>
+      </c>
+      <c r="B126" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C126" t="str">
+        <v>2026/9/26 11:08:06</v>
+      </c>
+      <c r="D126" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E126">
+        <v>200</v>
+      </c>
+      <c r="F126">
+        <v>3</v>
+      </c>
+      <c r="G126">
+        <v>600</v>
+      </c>
+      <c r="H126" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>#43</v>
+      </c>
+      <c r="B127" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C127" t="str">
+        <v>2026/9/26 11:08:06</v>
+      </c>
+      <c r="D127" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E127">
+        <v>200</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127">
+        <v>200</v>
+      </c>
+      <c r="H127" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>#43</v>
+      </c>
+      <c r="B128" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C128" t="str">
+        <v>2026/9/26 11:08:06</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E128">
+        <v>200</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>200</v>
+      </c>
+      <c r="H128" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>#43</v>
+      </c>
+      <c r="B129" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C129" t="str">
+        <v>2026/9/26 11:08:06</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E129">
+        <v>200</v>
+      </c>
+      <c r="F129">
+        <v>2</v>
+      </c>
+      <c r="G129">
+        <v>400</v>
+      </c>
+      <c r="H129" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>#43</v>
+      </c>
+      <c r="B130" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C130" t="str">
+        <v>2026/9/26 11:08:06</v>
+      </c>
+      <c r="D130" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E130">
+        <v>200</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130">
+        <v>200</v>
+      </c>
+      <c r="H130" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H125"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H130"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1940,16 +1940,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>#44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C45" t="str">
+        <v>2026/9/26 11:09:40</v>
+      </c>
+      <c r="D45" t="str">
+        <v>モンブラン×3, Iceコーヒー×1, Iceココア×1, 午後の紅茶 ミルクティー×1</v>
+      </c>
+      <c r="E45">
+        <v>1200</v>
+      </c>
+      <c r="F45">
+        <v>300</v>
+      </c>
+      <c r="G45">
+        <v>900</v>
+      </c>
+      <c r="H45">
+        <v>1000</v>
+      </c>
+      <c r="I45">
+        <v>100</v>
+      </c>
+      <c r="J45" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K45" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H134"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5331,9 +5366,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>#44</v>
+      </c>
+      <c r="B131" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C131" t="str">
+        <v>2026/9/26 11:09:40</v>
+      </c>
+      <c r="D131" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E131">
+        <v>200</v>
+      </c>
+      <c r="F131">
+        <v>3</v>
+      </c>
+      <c r="G131">
+        <v>600</v>
+      </c>
+      <c r="H131" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>#44</v>
+      </c>
+      <c r="B132" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C132" t="str">
+        <v>2026/9/26 11:09:40</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E132">
+        <v>200</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132">
+        <v>200</v>
+      </c>
+      <c r="H132" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>#44</v>
+      </c>
+      <c r="B133" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C133" t="str">
+        <v>2026/9/26 11:09:40</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E133">
+        <v>200</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133">
+        <v>200</v>
+      </c>
+      <c r="H133" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>#44</v>
+      </c>
+      <c r="B134" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C134" t="str">
+        <v>2026/9/26 11:09:40</v>
+      </c>
+      <c r="D134" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E134">
+        <v>200</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134">
+        <v>200</v>
+      </c>
+      <c r="H134" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H134"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1975,16 +1975,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>#45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C46" t="str">
+        <v>2026/9/26 11:10:34</v>
+      </c>
+      <c r="D46" t="str">
+        <v>午後の紅茶 ミルクティー×1</v>
+      </c>
+      <c r="E46">
+        <v>200</v>
+      </c>
+      <c r="F46">
+        <v>200</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>300</v>
+      </c>
+      <c r="I46">
+        <v>300</v>
+      </c>
+      <c r="J46" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K46" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K46"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H135"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5470,9 +5505,35 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>#45</v>
+      </c>
+      <c r="B135" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C135" t="str">
+        <v>2026/9/26 11:10:34</v>
+      </c>
+      <c r="D135" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E135">
+        <v>200</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135">
+        <v>200</v>
+      </c>
+      <c r="H135" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H134"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H135"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2010,16 +2010,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>#46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C47" t="str">
+        <v>2026/9/26 11:11:56</v>
+      </c>
+      <c r="D47" t="str">
+        <v>モンブラン×1, Hotココア×1, オレンジジュース×1</v>
+      </c>
+      <c r="E47">
+        <v>600</v>
+      </c>
+      <c r="F47">
+        <v>400</v>
+      </c>
+      <c r="G47">
+        <v>200</v>
+      </c>
+      <c r="H47">
+        <v>600</v>
+      </c>
+      <c r="I47">
+        <v>400</v>
+      </c>
+      <c r="J47" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K47" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K47"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H138"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5531,9 +5566,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>#46</v>
+      </c>
+      <c r="B136" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C136" t="str">
+        <v>2026/9/26 11:11:56</v>
+      </c>
+      <c r="D136" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E136">
+        <v>200</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136">
+        <v>200</v>
+      </c>
+      <c r="H136" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>#46</v>
+      </c>
+      <c r="B137" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C137" t="str">
+        <v>2026/9/26 11:11:56</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Hotココア</v>
+      </c>
+      <c r="E137">
+        <v>200</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="G137">
+        <v>200</v>
+      </c>
+      <c r="H137" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>#46</v>
+      </c>
+      <c r="B138" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C138" t="str">
+        <v>2026/9/26 11:11:56</v>
+      </c>
+      <c r="D138" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E138">
+        <v>200</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138">
+        <v>200</v>
+      </c>
+      <c r="H138" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H135"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H138"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K44" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2004,7 +2004,7 @@
         <v>300</v>
       </c>
       <c r="J46" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K46" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1969,7 +1969,7 @@
         <v>100</v>
       </c>
       <c r="J45" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K45" t="str">
         <v>iti</v>
@@ -2045,16 +2045,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>#47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C48" t="str">
+        <v>2026/9/26 11:13:35</v>
+      </c>
+      <c r="D48" t="str">
+        <v>メロンクリームソーダ×1</v>
+      </c>
+      <c r="E48">
+        <v>200</v>
+      </c>
+      <c r="F48">
+        <v>200</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>1000</v>
+      </c>
+      <c r="I48">
+        <v>1000</v>
+      </c>
+      <c r="J48" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K48" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K48"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H139"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5644,9 +5679,35 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>#47</v>
+      </c>
+      <c r="B139" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C139" t="str">
+        <v>2026/9/26 11:13:35</v>
+      </c>
+      <c r="D139" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E139">
+        <v>200</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="G139">
+        <v>200</v>
+      </c>
+      <c r="H139" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H138"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H139"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2039,7 +2039,7 @@
         <v>400</v>
       </c>
       <c r="J47" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K47" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2074,7 +2074,7 @@
         <v>1000</v>
       </c>
       <c r="J48" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K48" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2080,16 +2080,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>#48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C49" t="str">
+        <v>2026/9/26 11:20:11</v>
+      </c>
+      <c r="D49" t="str">
+        <v>クリームチーズタルト×1, チョコケーキ×2, 午後の紅茶 ミルクティー×2, オレンジジュース×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E49">
+        <v>1400</v>
+      </c>
+      <c r="F49">
+        <v>600</v>
+      </c>
+      <c r="G49">
+        <v>800</v>
+      </c>
+      <c r="H49">
+        <v>1500</v>
+      </c>
+      <c r="I49">
+        <v>700</v>
+      </c>
+      <c r="J49" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K49" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K49"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H144"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5705,9 +5740,139 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>#48</v>
+      </c>
+      <c r="B140" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C140" t="str">
+        <v>2026/9/26 11:20:11</v>
+      </c>
+      <c r="D140" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E140">
+        <v>200</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>200</v>
+      </c>
+      <c r="H140" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>#48</v>
+      </c>
+      <c r="B141" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C141" t="str">
+        <v>2026/9/26 11:20:11</v>
+      </c>
+      <c r="D141" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E141">
+        <v>200</v>
+      </c>
+      <c r="F141">
+        <v>2</v>
+      </c>
+      <c r="G141">
+        <v>400</v>
+      </c>
+      <c r="H141" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>#48</v>
+      </c>
+      <c r="B142" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C142" t="str">
+        <v>2026/9/26 11:20:11</v>
+      </c>
+      <c r="D142" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E142">
+        <v>200</v>
+      </c>
+      <c r="F142">
+        <v>2</v>
+      </c>
+      <c r="G142">
+        <v>400</v>
+      </c>
+      <c r="H142" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>#48</v>
+      </c>
+      <c r="B143" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C143" t="str">
+        <v>2026/9/26 11:20:11</v>
+      </c>
+      <c r="D143" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E143">
+        <v>200</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+      <c r="G143">
+        <v>200</v>
+      </c>
+      <c r="H143" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>#48</v>
+      </c>
+      <c r="B144" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C144" t="str">
+        <v>2026/9/26 11:20:11</v>
+      </c>
+      <c r="D144" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E144">
+        <v>200</v>
+      </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
+      <c r="G144">
+        <v>200</v>
+      </c>
+      <c r="H144" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H139"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H144"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2115,16 +2115,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>#49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C50" t="str">
+        <v>2026/9/26 11:20:31</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Hot紅茶×1</v>
+      </c>
+      <c r="E50">
+        <v>200</v>
+      </c>
+      <c r="F50">
+        <v>200</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K50" t="str">
+        <v>いち</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H145"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5870,9 +5905,35 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>#49</v>
+      </c>
+      <c r="B145" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C145" t="str">
+        <v>2026/9/26 11:20:31</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Hot紅茶</v>
+      </c>
+      <c r="E145">
+        <v>200</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="G145">
+        <v>200</v>
+      </c>
+      <c r="H145" t="str">
+        <v>いち</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H144"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H145"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K52"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2150,16 +2150,86 @@
         <v>いち</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>#50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C51" t="str">
+        <v>2026/9/26 11:22:04</v>
+      </c>
+      <c r="D51" t="str">
+        <v>カラメルカスタード×1, クリームチーズタルト×1, Iceコーヒー×2</v>
+      </c>
+      <c r="E51">
+        <v>800</v>
+      </c>
+      <c r="F51">
+        <v>200</v>
+      </c>
+      <c r="G51">
+        <v>600</v>
+      </c>
+      <c r="H51">
+        <v>600</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K51" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>#51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C52" t="str">
+        <v>2026/9/26 11:23:35</v>
+      </c>
+      <c r="D52" t="str">
+        <v>クリームチーズタルト×1</v>
+      </c>
+      <c r="E52">
+        <v>200</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>200</v>
+      </c>
+      <c r="H52">
+        <v>200</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K52" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K52"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H149"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5931,9 +6001,113 @@
         <v>いち</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>#50</v>
+      </c>
+      <c r="B146" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C146" t="str">
+        <v>2026/9/26 11:22:04</v>
+      </c>
+      <c r="D146" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E146">
+        <v>200</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146">
+        <v>200</v>
+      </c>
+      <c r="H146" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>#50</v>
+      </c>
+      <c r="B147" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C147" t="str">
+        <v>2026/9/26 11:22:04</v>
+      </c>
+      <c r="D147" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E147">
+        <v>200</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+      <c r="G147">
+        <v>200</v>
+      </c>
+      <c r="H147" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>#50</v>
+      </c>
+      <c r="B148" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C148" t="str">
+        <v>2026/9/26 11:22:04</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E148">
+        <v>200</v>
+      </c>
+      <c r="F148">
+        <v>2</v>
+      </c>
+      <c r="G148">
+        <v>400</v>
+      </c>
+      <c r="H148" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>#51</v>
+      </c>
+      <c r="B149" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C149" t="str">
+        <v>2026/9/26 11:23:35</v>
+      </c>
+      <c r="D149" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E149">
+        <v>200</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="G149">
+        <v>200</v>
+      </c>
+      <c r="H149" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H145"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H149"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2109,7 +2109,7 @@
         <v>700</v>
       </c>
       <c r="J49" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K49" t="str">
         <v>iti</v>
@@ -2220,16 +2220,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>#52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>席 14</v>
+      </c>
+      <c r="C53" t="str">
+        <v>2026/9/26 11:25:20</v>
+      </c>
+      <c r="D53" t="str">
+        <v>オレンジジュース×1</v>
+      </c>
+      <c r="E53">
+        <v>200</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>200</v>
+      </c>
+      <c r="H53">
+        <v>200</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K53" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K53"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H150"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6105,9 +6140,35 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>#52</v>
+      </c>
+      <c r="B150" t="str">
+        <v>席 14</v>
+      </c>
+      <c r="C150" t="str">
+        <v>2026/9/26 11:25:20</v>
+      </c>
+      <c r="D150" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E150">
+        <v>200</v>
+      </c>
+      <c r="F150">
+        <v>1</v>
+      </c>
+      <c r="G150">
+        <v>200</v>
+      </c>
+      <c r="H150" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H149"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H150"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K53" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K52" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K51" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2255,9 +2255,44 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>#53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>席 14</v>
+      </c>
+      <c r="C54" t="str">
+        <v>2026/9/26 11:27:47</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>200</v>
+      </c>
+      <c r="I54">
+        <v>200</v>
+      </c>
+      <c r="J54" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K54" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K54"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2290,16 +2290,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>#54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C55" t="str">
+        <v>2026/9/26 11:28:21</v>
+      </c>
+      <c r="D55" t="str">
+        <v>メロンクリームソーダ×1</v>
+      </c>
+      <c r="E55">
+        <v>200</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>200</v>
+      </c>
+      <c r="H55">
+        <v>200</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K55" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K55"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H151"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6201,9 +6236,35 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>#54</v>
+      </c>
+      <c r="B151" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C151" t="str">
+        <v>2026/9/26 11:28:21</v>
+      </c>
+      <c r="D151" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E151">
+        <v>200</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <v>200</v>
+      </c>
+      <c r="H151" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H150"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H151"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K55" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2325,16 +2325,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>#55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C56" t="str">
+        <v>2026/9/26 11:29:39</v>
+      </c>
+      <c r="D56" t="str">
+        <v>カラメルカスタード×1, モンブラン×1, クリームチーズタルト×1</v>
+      </c>
+      <c r="E56">
+        <v>600</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>600</v>
+      </c>
+      <c r="H56">
+        <v>600</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K56" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K56"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H154"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6262,9 +6297,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>#55</v>
+      </c>
+      <c r="B152" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C152" t="str">
+        <v>2026/9/26 11:29:39</v>
+      </c>
+      <c r="D152" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E152">
+        <v>200</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152">
+        <v>200</v>
+      </c>
+      <c r="H152" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>#55</v>
+      </c>
+      <c r="B153" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C153" t="str">
+        <v>2026/9/26 11:29:39</v>
+      </c>
+      <c r="D153" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E153">
+        <v>200</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+      <c r="G153">
+        <v>200</v>
+      </c>
+      <c r="H153" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>#55</v>
+      </c>
+      <c r="B154" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C154" t="str">
+        <v>2026/9/26 11:29:39</v>
+      </c>
+      <c r="D154" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E154">
+        <v>200</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154">
+        <v>200</v>
+      </c>
+      <c r="H154" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H154"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K58"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2360,16 +2360,86 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>#56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C57" t="str">
+        <v>2026/9/26 11:32:58</v>
+      </c>
+      <c r="D57" t="str">
+        <v>モンブラン×1, クリームチーズタルト×1, Hotコーヒー×2, 午後の紅茶 ミルクティー×1</v>
+      </c>
+      <c r="E57">
+        <v>1000</v>
+      </c>
+      <c r="F57">
+        <v>500</v>
+      </c>
+      <c r="G57">
+        <v>500</v>
+      </c>
+      <c r="H57">
+        <v>1000</v>
+      </c>
+      <c r="I57">
+        <v>500</v>
+      </c>
+      <c r="J57" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K57" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>#57</v>
+      </c>
+      <c r="B58" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C58" t="str">
+        <v>2026/9/26 11:34:15</v>
+      </c>
+      <c r="D58" t="str">
+        <v>モンブラン×1, クリームチーズタルト×1, Hotコーヒー×2</v>
+      </c>
+      <c r="E58">
+        <v>800</v>
+      </c>
+      <c r="F58">
+        <v>200</v>
+      </c>
+      <c r="G58">
+        <v>600</v>
+      </c>
+      <c r="H58">
+        <v>1000</v>
+      </c>
+      <c r="I58">
+        <v>400</v>
+      </c>
+      <c r="J58" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K58" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K58"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H161"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6375,9 +6445,191 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>#56</v>
+      </c>
+      <c r="B155" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C155" t="str">
+        <v>2026/9/26 11:32:58</v>
+      </c>
+      <c r="D155" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E155">
+        <v>200</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="G155">
+        <v>200</v>
+      </c>
+      <c r="H155" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>#56</v>
+      </c>
+      <c r="B156" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C156" t="str">
+        <v>2026/9/26 11:32:58</v>
+      </c>
+      <c r="D156" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E156">
+        <v>200</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156">
+        <v>200</v>
+      </c>
+      <c r="H156" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>#56</v>
+      </c>
+      <c r="B157" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C157" t="str">
+        <v>2026/9/26 11:32:58</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E157">
+        <v>200</v>
+      </c>
+      <c r="F157">
+        <v>2</v>
+      </c>
+      <c r="G157">
+        <v>400</v>
+      </c>
+      <c r="H157" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>#56</v>
+      </c>
+      <c r="B158" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C158" t="str">
+        <v>2026/9/26 11:32:58</v>
+      </c>
+      <c r="D158" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E158">
+        <v>200</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158">
+        <v>200</v>
+      </c>
+      <c r="H158" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>#57</v>
+      </c>
+      <c r="B159" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C159" t="str">
+        <v>2026/9/26 11:34:15</v>
+      </c>
+      <c r="D159" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E159">
+        <v>200</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159">
+        <v>200</v>
+      </c>
+      <c r="H159" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>#57</v>
+      </c>
+      <c r="B160" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C160" t="str">
+        <v>2026/9/26 11:34:15</v>
+      </c>
+      <c r="D160" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E160">
+        <v>200</v>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="G160">
+        <v>200</v>
+      </c>
+      <c r="H160" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>#57</v>
+      </c>
+      <c r="B161" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C161" t="str">
+        <v>2026/9/26 11:34:15</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E161">
+        <v>200</v>
+      </c>
+      <c r="F161">
+        <v>2</v>
+      </c>
+      <c r="G161">
+        <v>400</v>
+      </c>
+      <c r="H161" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H161"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2424,22 +2424,57 @@
         <v>400</v>
       </c>
       <c r="J58" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K58" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>#58</v>
+      </c>
+      <c r="B59" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C59" t="str">
+        <v>2026/9/26 11:36:13</v>
+      </c>
+      <c r="D59" t="str">
+        <v>チョコケーキ×1, プリンアラモード×1, 午後の紅茶 ミルクティー×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E59">
+        <v>800</v>
+      </c>
+      <c r="F59">
+        <v>200</v>
+      </c>
+      <c r="G59">
+        <v>600</v>
+      </c>
+      <c r="H59">
+        <v>600</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59" t="str">
         <v>提供待ち</v>
       </c>
-      <c r="K58" t="str">
+      <c r="K59" t="str">
         <v>iti</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K59"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H165"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6627,9 +6662,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>#58</v>
+      </c>
+      <c r="B162" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C162" t="str">
+        <v>2026/9/26 11:36:13</v>
+      </c>
+      <c r="D162" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E162">
+        <v>200</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="G162">
+        <v>200</v>
+      </c>
+      <c r="H162" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>#58</v>
+      </c>
+      <c r="B163" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C163" t="str">
+        <v>2026/9/26 11:36:13</v>
+      </c>
+      <c r="D163" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E163">
+        <v>200</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163">
+        <v>200</v>
+      </c>
+      <c r="H163" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>#58</v>
+      </c>
+      <c r="B164" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C164" t="str">
+        <v>2026/9/26 11:36:13</v>
+      </c>
+      <c r="D164" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E164">
+        <v>200</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+      <c r="G164">
+        <v>200</v>
+      </c>
+      <c r="H164" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>#58</v>
+      </c>
+      <c r="B165" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C165" t="str">
+        <v>2026/9/26 11:36:13</v>
+      </c>
+      <c r="D165" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E165">
+        <v>200</v>
+      </c>
+      <c r="F165">
+        <v>1</v>
+      </c>
+      <c r="G165">
+        <v>200</v>
+      </c>
+      <c r="H165" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H161"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H165"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2459,22 +2459,57 @@
         <v>0</v>
       </c>
       <c r="J59" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K59" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>#59</v>
+      </c>
+      <c r="B60" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C60" t="str">
+        <v>2026/9/26 11:37:09</v>
+      </c>
+      <c r="D60" t="str">
+        <v>クリームチーズタルト×1, Ice紅茶×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E60">
+        <v>600</v>
+      </c>
+      <c r="F60">
+        <v>400</v>
+      </c>
+      <c r="G60">
+        <v>200</v>
+      </c>
+      <c r="H60">
+        <v>600</v>
+      </c>
+      <c r="I60">
+        <v>400</v>
+      </c>
+      <c r="J60" t="str">
         <v>提供待ち</v>
       </c>
-      <c r="K59" t="str">
+      <c r="K60" t="str">
         <v>iti</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K60"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H168"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6766,9 +6801,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>#59</v>
+      </c>
+      <c r="B166" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C166" t="str">
+        <v>2026/9/26 11:37:09</v>
+      </c>
+      <c r="D166" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E166">
+        <v>200</v>
+      </c>
+      <c r="F166">
+        <v>1</v>
+      </c>
+      <c r="G166">
+        <v>200</v>
+      </c>
+      <c r="H166" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>#59</v>
+      </c>
+      <c r="B167" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C167" t="str">
+        <v>2026/9/26 11:37:09</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E167">
+        <v>200</v>
+      </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167">
+        <v>200</v>
+      </c>
+      <c r="H167" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>#59</v>
+      </c>
+      <c r="B168" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C168" t="str">
+        <v>2026/9/26 11:37:09</v>
+      </c>
+      <c r="D168" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E168">
+        <v>200</v>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168">
+        <v>200</v>
+      </c>
+      <c r="H168" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H165"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H168"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2494,7 +2494,7 @@
         <v>400</v>
       </c>
       <c r="J60" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K60" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2500,16 +2500,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>#60</v>
+      </c>
+      <c r="B61" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C61" t="str">
+        <v>2026/9/26 11:41:37</v>
+      </c>
+      <c r="D61" t="str">
+        <v>チョコケーキ×1, オレンジジュース×1</v>
+      </c>
+      <c r="E61">
+        <v>400</v>
+      </c>
+      <c r="F61">
+        <v>100</v>
+      </c>
+      <c r="G61">
+        <v>300</v>
+      </c>
+      <c r="H61">
+        <v>300</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K61" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K61"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H170"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6879,9 +6914,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>#60</v>
+      </c>
+      <c r="B169" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C169" t="str">
+        <v>2026/9/26 11:41:37</v>
+      </c>
+      <c r="D169" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E169">
+        <v>200</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169">
+        <v>200</v>
+      </c>
+      <c r="H169" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>#60</v>
+      </c>
+      <c r="B170" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C170" t="str">
+        <v>2026/9/26 11:41:37</v>
+      </c>
+      <c r="D170" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E170">
+        <v>200</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170">
+        <v>200</v>
+      </c>
+      <c r="H170" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H168"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H170"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2535,16 +2535,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>#61</v>
+      </c>
+      <c r="B62" t="str">
+        <v>席 13</v>
+      </c>
+      <c r="C62" t="str">
+        <v>2026/9/26 11:41:54</v>
+      </c>
+      <c r="D62" t="str">
+        <v>プリンアラモード×1, 午後の紅茶 ミルクティー×1</v>
+      </c>
+      <c r="E62">
+        <v>400</v>
+      </c>
+      <c r="F62">
+        <v>100</v>
+      </c>
+      <c r="G62">
+        <v>300</v>
+      </c>
+      <c r="H62">
+        <v>300</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K62" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K62"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H172"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6966,9 +7001,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>#61</v>
+      </c>
+      <c r="B171" t="str">
+        <v>席 13</v>
+      </c>
+      <c r="C171" t="str">
+        <v>2026/9/26 11:41:54</v>
+      </c>
+      <c r="D171" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E171">
+        <v>200</v>
+      </c>
+      <c r="F171">
+        <v>1</v>
+      </c>
+      <c r="G171">
+        <v>200</v>
+      </c>
+      <c r="H171" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>#61</v>
+      </c>
+      <c r="B172" t="str">
+        <v>席 13</v>
+      </c>
+      <c r="C172" t="str">
+        <v>2026/9/26 11:41:54</v>
+      </c>
+      <c r="D172" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E172">
+        <v>200</v>
+      </c>
+      <c r="F172">
+        <v>1</v>
+      </c>
+      <c r="G172">
+        <v>200</v>
+      </c>
+      <c r="H172" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H170"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H172"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K61" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2570,16 +2570,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>#62</v>
+      </c>
+      <c r="B63" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C63" t="str">
+        <v>2026/9/26 11:43:54</v>
+      </c>
+      <c r="D63" t="str">
+        <v>モンブラン×1, チョコケーキ×1, Hotコーヒー×1, メロンクリームソーダ×1</v>
+      </c>
+      <c r="E63">
+        <v>800</v>
+      </c>
+      <c r="F63">
+        <v>200</v>
+      </c>
+      <c r="G63">
+        <v>600</v>
+      </c>
+      <c r="H63">
+        <v>1000</v>
+      </c>
+      <c r="I63">
+        <v>400</v>
+      </c>
+      <c r="J63" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K63" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K63"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H176"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7053,9 +7088,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>#62</v>
+      </c>
+      <c r="B173" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C173" t="str">
+        <v>2026/9/26 11:43:54</v>
+      </c>
+      <c r="D173" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E173">
+        <v>200</v>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="G173">
+        <v>200</v>
+      </c>
+      <c r="H173" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>#62</v>
+      </c>
+      <c r="B174" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C174" t="str">
+        <v>2026/9/26 11:43:54</v>
+      </c>
+      <c r="D174" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E174">
+        <v>200</v>
+      </c>
+      <c r="F174">
+        <v>1</v>
+      </c>
+      <c r="G174">
+        <v>200</v>
+      </c>
+      <c r="H174" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>#62</v>
+      </c>
+      <c r="B175" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C175" t="str">
+        <v>2026/9/26 11:43:54</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E175">
+        <v>200</v>
+      </c>
+      <c r="F175">
+        <v>1</v>
+      </c>
+      <c r="G175">
+        <v>200</v>
+      </c>
+      <c r="H175" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>#62</v>
+      </c>
+      <c r="B176" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C176" t="str">
+        <v>2026/9/26 11:43:54</v>
+      </c>
+      <c r="D176" t="str">
+        <v>メロンクリームソーダ</v>
+      </c>
+      <c r="E176">
+        <v>200</v>
+      </c>
+      <c r="F176">
+        <v>1</v>
+      </c>
+      <c r="G176">
+        <v>200</v>
+      </c>
+      <c r="H176" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H172"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H176"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2605,16 +2605,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>#63</v>
+      </c>
+      <c r="B64" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C64" t="str">
+        <v>2026/9/26 11:45:01</v>
+      </c>
+      <c r="D64" t="str">
+        <v>カラメルカスタード×2, モンブラン×1, Iceコーヒー×2, 午後の紅茶 ミルクティー×1</v>
+      </c>
+      <c r="E64">
+        <v>1200</v>
+      </c>
+      <c r="F64">
+        <v>300</v>
+      </c>
+      <c r="G64">
+        <v>900</v>
+      </c>
+      <c r="H64">
+        <v>900</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K64" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K64"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H180"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7192,9 +7227,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>#63</v>
+      </c>
+      <c r="B177" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C177" t="str">
+        <v>2026/9/26 11:45:01</v>
+      </c>
+      <c r="D177" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E177">
+        <v>200</v>
+      </c>
+      <c r="F177">
+        <v>2</v>
+      </c>
+      <c r="G177">
+        <v>400</v>
+      </c>
+      <c r="H177" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>#63</v>
+      </c>
+      <c r="B178" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C178" t="str">
+        <v>2026/9/26 11:45:01</v>
+      </c>
+      <c r="D178" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E178">
+        <v>200</v>
+      </c>
+      <c r="F178">
+        <v>1</v>
+      </c>
+      <c r="G178">
+        <v>200</v>
+      </c>
+      <c r="H178" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>#63</v>
+      </c>
+      <c r="B179" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C179" t="str">
+        <v>2026/9/26 11:45:01</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E179">
+        <v>200</v>
+      </c>
+      <c r="F179">
+        <v>2</v>
+      </c>
+      <c r="G179">
+        <v>400</v>
+      </c>
+      <c r="H179" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>#63</v>
+      </c>
+      <c r="B180" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C180" t="str">
+        <v>2026/9/26 11:45:01</v>
+      </c>
+      <c r="D180" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E180">
+        <v>200</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180">
+        <v>200</v>
+      </c>
+      <c r="H180" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H176"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H180"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="J62" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K62" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K65"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2640,16 +2640,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>#64</v>
+      </c>
+      <c r="B65" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C65" t="str">
+        <v>2026/9/26 11:46:03</v>
+      </c>
+      <c r="D65" t="str">
+        <v>モンブラン×1, Iceコーヒー×1</v>
+      </c>
+      <c r="E65">
+        <v>400</v>
+      </c>
+      <c r="F65">
+        <v>100</v>
+      </c>
+      <c r="G65">
+        <v>300</v>
+      </c>
+      <c r="H65">
+        <v>300</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K65" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K65"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H182"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7331,9 +7366,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>#64</v>
+      </c>
+      <c r="B181" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C181" t="str">
+        <v>2026/9/26 11:46:03</v>
+      </c>
+      <c r="D181" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E181">
+        <v>200</v>
+      </c>
+      <c r="F181">
+        <v>1</v>
+      </c>
+      <c r="G181">
+        <v>200</v>
+      </c>
+      <c r="H181" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>#64</v>
+      </c>
+      <c r="B182" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C182" t="str">
+        <v>2026/9/26 11:46:03</v>
+      </c>
+      <c r="D182" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E182">
+        <v>200</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182">
+        <v>200</v>
+      </c>
+      <c r="H182" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H180"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H182"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K66"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2599,7 +2599,7 @@
         <v>400</v>
       </c>
       <c r="J63" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K63" t="str">
         <v>iti</v>
@@ -2675,16 +2675,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>#65</v>
+      </c>
+      <c r="B66" t="str">
+        <v>席 12</v>
+      </c>
+      <c r="C66" t="str">
+        <v>2026/9/26 11:48:04</v>
+      </c>
+      <c r="D66" t="str">
+        <v>チョコケーキ×1, プリンアラモード×1, オレンジジュース×1</v>
+      </c>
+      <c r="E66">
+        <v>600</v>
+      </c>
+      <c r="F66">
+        <v>100</v>
+      </c>
+      <c r="G66">
+        <v>500</v>
+      </c>
+      <c r="H66">
+        <v>500</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K66" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K66"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H185"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7418,9 +7453,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>#65</v>
+      </c>
+      <c r="B183" t="str">
+        <v>席 12</v>
+      </c>
+      <c r="C183" t="str">
+        <v>2026/9/26 11:48:04</v>
+      </c>
+      <c r="D183" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E183">
+        <v>200</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+      <c r="G183">
+        <v>200</v>
+      </c>
+      <c r="H183" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>#65</v>
+      </c>
+      <c r="B184" t="str">
+        <v>席 12</v>
+      </c>
+      <c r="C184" t="str">
+        <v>2026/9/26 11:48:04</v>
+      </c>
+      <c r="D184" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E184">
+        <v>200</v>
+      </c>
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184">
+        <v>200</v>
+      </c>
+      <c r="H184" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>#65</v>
+      </c>
+      <c r="B185" t="str">
+        <v>席 12</v>
+      </c>
+      <c r="C185" t="str">
+        <v>2026/9/26 11:48:04</v>
+      </c>
+      <c r="D185" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E185">
+        <v>200</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185">
+        <v>200</v>
+      </c>
+      <c r="H185" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H182"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H185"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K67"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2710,16 +2710,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>#66</v>
+      </c>
+      <c r="B67" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C67" t="str">
+        <v>2026/9/26 11:50:50</v>
+      </c>
+      <c r="D67" t="str">
+        <v>クリームチーズタルト×1, Iceコーヒー×2</v>
+      </c>
+      <c r="E67">
+        <v>600</v>
+      </c>
+      <c r="F67">
+        <v>400</v>
+      </c>
+      <c r="G67">
+        <v>200</v>
+      </c>
+      <c r="H67">
+        <v>1300</v>
+      </c>
+      <c r="I67">
+        <v>1100</v>
+      </c>
+      <c r="J67" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K67" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K67"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H187"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7531,9 +7566,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>#66</v>
+      </c>
+      <c r="B186" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C186" t="str">
+        <v>2026/9/26 11:50:50</v>
+      </c>
+      <c r="D186" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E186">
+        <v>200</v>
+      </c>
+      <c r="F186">
+        <v>1</v>
+      </c>
+      <c r="G186">
+        <v>200</v>
+      </c>
+      <c r="H186" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>#66</v>
+      </c>
+      <c r="B187" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C187" t="str">
+        <v>2026/9/26 11:50:50</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E187">
+        <v>200</v>
+      </c>
+      <c r="F187">
+        <v>2</v>
+      </c>
+      <c r="G187">
+        <v>400</v>
+      </c>
+      <c r="H187" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H185"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H187"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K64" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2739,7 +2739,7 @@
         <v>1100</v>
       </c>
       <c r="J67" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K67" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2704,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K66" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K65" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K69"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2745,16 +2745,86 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>#67</v>
+      </c>
+      <c r="B68" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C68" t="str">
+        <v>2026/9/26 11:51:57</v>
+      </c>
+      <c r="D68" t="str">
+        <v>モンブラン×2, クリームチーズタルト×1</v>
+      </c>
+      <c r="E68">
+        <v>600</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>600</v>
+      </c>
+      <c r="H68">
+        <v>1400</v>
+      </c>
+      <c r="I68">
+        <v>800</v>
+      </c>
+      <c r="J68" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K68" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>#68</v>
+      </c>
+      <c r="B69" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C69" t="str">
+        <v>2026/9/26 11:52:54</v>
+      </c>
+      <c r="D69" t="str">
+        <v>モンブラン×1, Hotコーヒー×1, オレンジジュース×1</v>
+      </c>
+      <c r="E69">
+        <v>600</v>
+      </c>
+      <c r="F69">
+        <v>400</v>
+      </c>
+      <c r="G69">
+        <v>200</v>
+      </c>
+      <c r="H69">
+        <v>600</v>
+      </c>
+      <c r="I69">
+        <v>400</v>
+      </c>
+      <c r="J69" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K69" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K69"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H192"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7618,9 +7688,139 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>#67</v>
+      </c>
+      <c r="B188" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C188" t="str">
+        <v>2026/9/26 11:51:57</v>
+      </c>
+      <c r="D188" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E188">
+        <v>200</v>
+      </c>
+      <c r="F188">
+        <v>2</v>
+      </c>
+      <c r="G188">
+        <v>400</v>
+      </c>
+      <c r="H188" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>#67</v>
+      </c>
+      <c r="B189" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C189" t="str">
+        <v>2026/9/26 11:51:57</v>
+      </c>
+      <c r="D189" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E189">
+        <v>200</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189">
+        <v>200</v>
+      </c>
+      <c r="H189" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>#68</v>
+      </c>
+      <c r="B190" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C190" t="str">
+        <v>2026/9/26 11:52:54</v>
+      </c>
+      <c r="D190" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E190">
+        <v>200</v>
+      </c>
+      <c r="F190">
+        <v>1</v>
+      </c>
+      <c r="G190">
+        <v>200</v>
+      </c>
+      <c r="H190" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>#68</v>
+      </c>
+      <c r="B191" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C191" t="str">
+        <v>2026/9/26 11:52:54</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E191">
+        <v>200</v>
+      </c>
+      <c r="F191">
+        <v>1</v>
+      </c>
+      <c r="G191">
+        <v>200</v>
+      </c>
+      <c r="H191" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>#68</v>
+      </c>
+      <c r="B192" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C192" t="str">
+        <v>2026/9/26 11:52:54</v>
+      </c>
+      <c r="D192" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E192">
+        <v>200</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+      <c r="G192">
+        <v>200</v>
+      </c>
+      <c r="H192" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H187"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H192"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2774,7 +2774,7 @@
         <v>800</v>
       </c>
       <c r="J68" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K68" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2809,7 +2809,7 @@
         <v>400</v>
       </c>
       <c r="J69" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K69" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2815,16 +2815,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>#69</v>
+      </c>
+      <c r="B70" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C70" t="str">
+        <v>2026/9/26 11:58:49</v>
+      </c>
+      <c r="D70" t="str">
+        <v>カラメルカスタード×1, カフェオレ(Hot)×1</v>
+      </c>
+      <c r="E70">
+        <v>400</v>
+      </c>
+      <c r="F70">
+        <v>100</v>
+      </c>
+      <c r="G70">
+        <v>300</v>
+      </c>
+      <c r="H70">
+        <v>1000</v>
+      </c>
+      <c r="I70">
+        <v>700</v>
+      </c>
+      <c r="J70" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K70" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K70"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H194"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7818,9 +7853,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>#69</v>
+      </c>
+      <c r="B193" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C193" t="str">
+        <v>2026/9/26 11:58:49</v>
+      </c>
+      <c r="D193" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E193">
+        <v>200</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+      <c r="G193">
+        <v>200</v>
+      </c>
+      <c r="H193" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>#69</v>
+      </c>
+      <c r="B194" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C194" t="str">
+        <v>2026/9/26 11:58:49</v>
+      </c>
+      <c r="D194" t="str">
+        <v>カフェオレ(Hot)</v>
+      </c>
+      <c r="E194">
+        <v>200</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+      <c r="G194">
+        <v>200</v>
+      </c>
+      <c r="H194" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H192"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H194"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K72"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2850,16 +2850,86 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>#70</v>
+      </c>
+      <c r="B71" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C71" t="str">
+        <v>2026/9/26 12:00:05</v>
+      </c>
+      <c r="D71" t="str">
+        <v>プリンアラモード×1</v>
+      </c>
+      <c r="E71">
+        <v>200</v>
+      </c>
+      <c r="F71">
+        <v>200</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>400</v>
+      </c>
+      <c r="I71">
+        <v>400</v>
+      </c>
+      <c r="J71" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K71" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>#71</v>
+      </c>
+      <c r="B72" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C72" t="str">
+        <v>2026/9/26 12:02:17</v>
+      </c>
+      <c r="D72" t="str">
+        <v>モンブラン×1, カフェオレ(Hot)×1</v>
+      </c>
+      <c r="E72">
+        <v>400</v>
+      </c>
+      <c r="F72">
+        <v>100</v>
+      </c>
+      <c r="G72">
+        <v>300</v>
+      </c>
+      <c r="H72">
+        <v>1000</v>
+      </c>
+      <c r="I72">
+        <v>700</v>
+      </c>
+      <c r="J72" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K72" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K72"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H194"/>
+  <dimension ref="A1:H197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7905,9 +7975,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>#70</v>
+      </c>
+      <c r="B195" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C195" t="str">
+        <v>2026/9/26 12:00:05</v>
+      </c>
+      <c r="D195" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E195">
+        <v>200</v>
+      </c>
+      <c r="F195">
+        <v>1</v>
+      </c>
+      <c r="G195">
+        <v>200</v>
+      </c>
+      <c r="H195" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>#71</v>
+      </c>
+      <c r="B196" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C196" t="str">
+        <v>2026/9/26 12:02:17</v>
+      </c>
+      <c r="D196" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E196">
+        <v>200</v>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+      <c r="G196">
+        <v>200</v>
+      </c>
+      <c r="H196" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>#71</v>
+      </c>
+      <c r="B197" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C197" t="str">
+        <v>2026/9/26 12:02:17</v>
+      </c>
+      <c r="D197" t="str">
+        <v>カフェオレ(Hot)</v>
+      </c>
+      <c r="E197">
+        <v>200</v>
+      </c>
+      <c r="F197">
+        <v>1</v>
+      </c>
+      <c r="G197">
+        <v>200</v>
+      </c>
+      <c r="H197" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H194"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H197"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K73"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2914,22 +2914,57 @@
         <v>700</v>
       </c>
       <c r="J72" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K72" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>#72</v>
+      </c>
+      <c r="B73" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C73" t="str">
+        <v>2026/9/26 12:04:36</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Iceココア×2</v>
+      </c>
+      <c r="E73">
+        <v>400</v>
+      </c>
+      <c r="F73">
+        <v>400</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>1000</v>
+      </c>
+      <c r="I73">
+        <v>1000</v>
+      </c>
+      <c r="J73" t="str">
         <v>提供待ち</v>
       </c>
-      <c r="K72" t="str">
+      <c r="K73" t="str">
         <v>iti</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K73"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H197"/>
+  <dimension ref="A1:H198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8053,9 +8088,35 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>#72</v>
+      </c>
+      <c r="B198" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C198" t="str">
+        <v>2026/9/26 12:04:36</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E198">
+        <v>200</v>
+      </c>
+      <c r="F198">
+        <v>2</v>
+      </c>
+      <c r="G198">
+        <v>400</v>
+      </c>
+      <c r="H198" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H197"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -2949,7 +2949,7 @@
         <v>1000</v>
       </c>
       <c r="J73" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K73" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K74"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2955,16 +2955,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>#73</v>
+      </c>
+      <c r="B74" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C74" t="str">
+        <v>2026/9/26 12:09:08</v>
+      </c>
+      <c r="D74" t="str">
+        <v>クリームチーズタルト×1, 午後の紅茶 ミルクティー×1, オレンジジュース×1</v>
+      </c>
+      <c r="E74">
+        <v>600</v>
+      </c>
+      <c r="F74">
+        <v>400</v>
+      </c>
+      <c r="G74">
+        <v>200</v>
+      </c>
+      <c r="H74">
+        <v>600</v>
+      </c>
+      <c r="I74">
+        <v>400</v>
+      </c>
+      <c r="J74" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K74" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K73"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K74"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8114,9 +8149,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>#73</v>
+      </c>
+      <c r="B199" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C199" t="str">
+        <v>2026/9/26 12:09:08</v>
+      </c>
+      <c r="D199" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E199">
+        <v>200</v>
+      </c>
+      <c r="F199">
+        <v>1</v>
+      </c>
+      <c r="G199">
+        <v>200</v>
+      </c>
+      <c r="H199" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>#73</v>
+      </c>
+      <c r="B200" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C200" t="str">
+        <v>2026/9/26 12:09:08</v>
+      </c>
+      <c r="D200" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E200">
+        <v>200</v>
+      </c>
+      <c r="F200">
+        <v>1</v>
+      </c>
+      <c r="G200">
+        <v>200</v>
+      </c>
+      <c r="H200" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>#73</v>
+      </c>
+      <c r="B201" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C201" t="str">
+        <v>2026/9/26 12:09:08</v>
+      </c>
+      <c r="D201" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E201">
+        <v>200</v>
+      </c>
+      <c r="F201">
+        <v>1</v>
+      </c>
+      <c r="G201">
+        <v>200</v>
+      </c>
+      <c r="H201" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K75"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2990,16 +2990,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>#74</v>
+      </c>
+      <c r="B75" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C75" t="str">
+        <v>2026/9/26 12:10:50</v>
+      </c>
+      <c r="D75" t="str">
+        <v>モンブラン×1, Hotコーヒー×1</v>
+      </c>
+      <c r="E75">
+        <v>400</v>
+      </c>
+      <c r="F75">
+        <v>100</v>
+      </c>
+      <c r="G75">
+        <v>300</v>
+      </c>
+      <c r="H75">
+        <v>500</v>
+      </c>
+      <c r="I75">
+        <v>200</v>
+      </c>
+      <c r="J75" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K75" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K74"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K75"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:H203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8227,9 +8262,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>#74</v>
+      </c>
+      <c r="B202" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C202" t="str">
+        <v>2026/9/26 12:10:50</v>
+      </c>
+      <c r="D202" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E202">
+        <v>200</v>
+      </c>
+      <c r="F202">
+        <v>1</v>
+      </c>
+      <c r="G202">
+        <v>200</v>
+      </c>
+      <c r="H202" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>#74</v>
+      </c>
+      <c r="B203" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C203" t="str">
+        <v>2026/9/26 12:10:50</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E203">
+        <v>200</v>
+      </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
+      <c r="G203">
+        <v>200</v>
+      </c>
+      <c r="H203" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H203"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K77"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3025,16 +3025,86 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>#75</v>
+      </c>
+      <c r="B76" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C76" t="str">
+        <v>2026/9/26 12:13:17</v>
+      </c>
+      <c r="D76" t="str">
+        <v>カラメルカスタード×1, チョコケーキ×1, Iceコーヒー×1, Ice紅茶×2, 午後の紅茶 ミルクティー×1</v>
+      </c>
+      <c r="E76">
+        <v>1200</v>
+      </c>
+      <c r="F76">
+        <v>200</v>
+      </c>
+      <c r="G76">
+        <v>1000</v>
+      </c>
+      <c r="H76">
+        <v>1000</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K76" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>#76</v>
+      </c>
+      <c r="B77" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C77" t="str">
+        <v>2026/9/26 12:14:26</v>
+      </c>
+      <c r="D77" t="str">
+        <v>プリンアラモード×1, Ice紅茶×2</v>
+      </c>
+      <c r="E77">
+        <v>600</v>
+      </c>
+      <c r="F77">
+        <v>400</v>
+      </c>
+      <c r="G77">
+        <v>200</v>
+      </c>
+      <c r="H77">
+        <v>600</v>
+      </c>
+      <c r="I77">
+        <v>400</v>
+      </c>
+      <c r="J77" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K77" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K75"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K77"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H210"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8314,9 +8384,191 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>#75</v>
+      </c>
+      <c r="B204" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C204" t="str">
+        <v>2026/9/26 12:13:17</v>
+      </c>
+      <c r="D204" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E204">
+        <v>200</v>
+      </c>
+      <c r="F204">
+        <v>1</v>
+      </c>
+      <c r="G204">
+        <v>200</v>
+      </c>
+      <c r="H204" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>#75</v>
+      </c>
+      <c r="B205" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C205" t="str">
+        <v>2026/9/26 12:13:17</v>
+      </c>
+      <c r="D205" t="str">
+        <v>チョコケーキ</v>
+      </c>
+      <c r="E205">
+        <v>200</v>
+      </c>
+      <c r="F205">
+        <v>1</v>
+      </c>
+      <c r="G205">
+        <v>200</v>
+      </c>
+      <c r="H205" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>#75</v>
+      </c>
+      <c r="B206" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C206" t="str">
+        <v>2026/9/26 12:13:17</v>
+      </c>
+      <c r="D206" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E206">
+        <v>200</v>
+      </c>
+      <c r="F206">
+        <v>1</v>
+      </c>
+      <c r="G206">
+        <v>200</v>
+      </c>
+      <c r="H206" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>#75</v>
+      </c>
+      <c r="B207" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C207" t="str">
+        <v>2026/9/26 12:13:17</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E207">
+        <v>200</v>
+      </c>
+      <c r="F207">
+        <v>2</v>
+      </c>
+      <c r="G207">
+        <v>400</v>
+      </c>
+      <c r="H207" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>#75</v>
+      </c>
+      <c r="B208" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C208" t="str">
+        <v>2026/9/26 12:13:17</v>
+      </c>
+      <c r="D208" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E208">
+        <v>200</v>
+      </c>
+      <c r="F208">
+        <v>1</v>
+      </c>
+      <c r="G208">
+        <v>200</v>
+      </c>
+      <c r="H208" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>#76</v>
+      </c>
+      <c r="B209" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C209" t="str">
+        <v>2026/9/26 12:14:26</v>
+      </c>
+      <c r="D209" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E209">
+        <v>200</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209">
+        <v>200</v>
+      </c>
+      <c r="H209" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>#76</v>
+      </c>
+      <c r="B210" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C210" t="str">
+        <v>2026/9/26 12:14:26</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E210">
+        <v>200</v>
+      </c>
+      <c r="F210">
+        <v>2</v>
+      </c>
+      <c r="G210">
+        <v>400</v>
+      </c>
+      <c r="H210" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H210"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K79"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3095,16 +3095,86 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>#77</v>
+      </c>
+      <c r="B78" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C78" t="str">
+        <v>2026/9/26 12:16:07</v>
+      </c>
+      <c r="D78" t="str">
+        <v>モンブラン×1, クリームチーズタルト×1, プリンアラモード×2</v>
+      </c>
+      <c r="E78">
+        <v>800</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>800</v>
+      </c>
+      <c r="H78">
+        <v>800</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K78" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>#78</v>
+      </c>
+      <c r="B79" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C79" t="str">
+        <v>2026/9/26 12:16:51</v>
+      </c>
+      <c r="D79" t="str">
+        <v>モンブラン×1, クリームチーズタルト×1, Iceコーヒー×1, オレンジジュース×1</v>
+      </c>
+      <c r="E79">
+        <v>800</v>
+      </c>
+      <c r="F79">
+        <v>200</v>
+      </c>
+      <c r="G79">
+        <v>600</v>
+      </c>
+      <c r="H79">
+        <v>600</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K79" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K77"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K79"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:H217"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8566,9 +8636,191 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>#77</v>
+      </c>
+      <c r="B211" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C211" t="str">
+        <v>2026/9/26 12:16:07</v>
+      </c>
+      <c r="D211" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E211">
+        <v>200</v>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+      <c r="G211">
+        <v>200</v>
+      </c>
+      <c r="H211" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>#77</v>
+      </c>
+      <c r="B212" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C212" t="str">
+        <v>2026/9/26 12:16:07</v>
+      </c>
+      <c r="D212" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E212">
+        <v>200</v>
+      </c>
+      <c r="F212">
+        <v>1</v>
+      </c>
+      <c r="G212">
+        <v>200</v>
+      </c>
+      <c r="H212" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>#77</v>
+      </c>
+      <c r="B213" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C213" t="str">
+        <v>2026/9/26 12:16:07</v>
+      </c>
+      <c r="D213" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E213">
+        <v>200</v>
+      </c>
+      <c r="F213">
+        <v>2</v>
+      </c>
+      <c r="G213">
+        <v>400</v>
+      </c>
+      <c r="H213" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>#78</v>
+      </c>
+      <c r="B214" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C214" t="str">
+        <v>2026/9/26 12:16:51</v>
+      </c>
+      <c r="D214" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E214">
+        <v>200</v>
+      </c>
+      <c r="F214">
+        <v>1</v>
+      </c>
+      <c r="G214">
+        <v>200</v>
+      </c>
+      <c r="H214" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>#78</v>
+      </c>
+      <c r="B215" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C215" t="str">
+        <v>2026/9/26 12:16:51</v>
+      </c>
+      <c r="D215" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E215">
+        <v>200</v>
+      </c>
+      <c r="F215">
+        <v>1</v>
+      </c>
+      <c r="G215">
+        <v>200</v>
+      </c>
+      <c r="H215" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>#78</v>
+      </c>
+      <c r="B216" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C216" t="str">
+        <v>2026/9/26 12:16:51</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E216">
+        <v>200</v>
+      </c>
+      <c r="F216">
+        <v>1</v>
+      </c>
+      <c r="G216">
+        <v>200</v>
+      </c>
+      <c r="H216" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>#78</v>
+      </c>
+      <c r="B217" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C217" t="str">
+        <v>2026/9/26 12:16:51</v>
+      </c>
+      <c r="D217" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E217">
+        <v>200</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+      <c r="G217">
+        <v>200</v>
+      </c>
+      <c r="H217" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H210"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H217"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -3089,7 +3089,7 @@
         <v>400</v>
       </c>
       <c r="J77" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K77" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K80"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3165,16 +3165,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>#79</v>
+      </c>
+      <c r="B80" t="str">
+        <v>席 11</v>
+      </c>
+      <c r="C80" t="str">
+        <v>2026/9/26 12:21:04</v>
+      </c>
+      <c r="D80" t="str">
+        <v>モンブラン×1, オレンジジュース×1</v>
+      </c>
+      <c r="E80">
+        <v>400</v>
+      </c>
+      <c r="F80">
+        <v>100</v>
+      </c>
+      <c r="G80">
+        <v>300</v>
+      </c>
+      <c r="H80">
+        <v>300</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K80" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K80"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H217"/>
+  <dimension ref="A1:H219"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8818,9 +8853,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>#79</v>
+      </c>
+      <c r="B218" t="str">
+        <v>席 11</v>
+      </c>
+      <c r="C218" t="str">
+        <v>2026/9/26 12:21:04</v>
+      </c>
+      <c r="D218" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E218">
+        <v>200</v>
+      </c>
+      <c r="F218">
+        <v>1</v>
+      </c>
+      <c r="G218">
+        <v>200</v>
+      </c>
+      <c r="H218" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>#79</v>
+      </c>
+      <c r="B219" t="str">
+        <v>席 11</v>
+      </c>
+      <c r="C219" t="str">
+        <v>2026/9/26 12:21:04</v>
+      </c>
+      <c r="D219" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E219">
+        <v>200</v>
+      </c>
+      <c r="F219">
+        <v>1</v>
+      </c>
+      <c r="G219">
+        <v>200</v>
+      </c>
+      <c r="H219" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H217"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H219"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K81"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3200,16 +3200,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>#80</v>
+      </c>
+      <c r="B81" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C81" t="str">
+        <v>2026/9/26 12:22:52</v>
+      </c>
+      <c r="D81" t="str">
+        <v>クリームチーズタルト×2, オレンジジュース×2</v>
+      </c>
+      <c r="E81">
+        <v>800</v>
+      </c>
+      <c r="F81">
+        <v>200</v>
+      </c>
+      <c r="G81">
+        <v>600</v>
+      </c>
+      <c r="H81">
+        <v>1500</v>
+      </c>
+      <c r="I81">
+        <v>900</v>
+      </c>
+      <c r="J81" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K81" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K80"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K81"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H219"/>
+  <dimension ref="A1:H221"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8905,9 +8940,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>#80</v>
+      </c>
+      <c r="B220" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C220" t="str">
+        <v>2026/9/26 12:22:52</v>
+      </c>
+      <c r="D220" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E220">
+        <v>200</v>
+      </c>
+      <c r="F220">
+        <v>2</v>
+      </c>
+      <c r="G220">
+        <v>400</v>
+      </c>
+      <c r="H220" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>#80</v>
+      </c>
+      <c r="B221" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C221" t="str">
+        <v>2026/9/26 12:22:52</v>
+      </c>
+      <c r="D221" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E221">
+        <v>200</v>
+      </c>
+      <c r="F221">
+        <v>2</v>
+      </c>
+      <c r="G221">
+        <v>400</v>
+      </c>
+      <c r="H221" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H219"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H221"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K78" t="str">
         <v>iti</v>
@@ -3194,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K80" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3235,16 +3235,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>#81</v>
+      </c>
+      <c r="B82" t="str">
+        <v>席 14</v>
+      </c>
+      <c r="C82" t="str">
+        <v>2026/9/26 12:24:14</v>
+      </c>
+      <c r="D82" t="str">
+        <v>プリンアラモード×1, Ice紅茶×1</v>
+      </c>
+      <c r="E82">
+        <v>400</v>
+      </c>
+      <c r="F82">
+        <v>100</v>
+      </c>
+      <c r="G82">
+        <v>300</v>
+      </c>
+      <c r="H82">
+        <v>300</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K82" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K82"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H221"/>
+  <dimension ref="A1:H223"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8992,9 +9027,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>#81</v>
+      </c>
+      <c r="B222" t="str">
+        <v>席 14</v>
+      </c>
+      <c r="C222" t="str">
+        <v>2026/9/26 12:24:14</v>
+      </c>
+      <c r="D222" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E222">
+        <v>200</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222">
+        <v>200</v>
+      </c>
+      <c r="H222" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>#81</v>
+      </c>
+      <c r="B223" t="str">
+        <v>席 14</v>
+      </c>
+      <c r="C223" t="str">
+        <v>2026/9/26 12:24:14</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E223">
+        <v>200</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
+      </c>
+      <c r="G223">
+        <v>200</v>
+      </c>
+      <c r="H223" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H221"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H223"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -3229,7 +3229,7 @@
         <v>900</v>
       </c>
       <c r="J81" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K81" t="str">
         <v>iti</v>
@@ -3264,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K82" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3270,16 +3270,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>#82</v>
+      </c>
+      <c r="B83" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C83" t="str">
+        <v>2026/9/26 12:30:07</v>
+      </c>
+      <c r="D83" t="str">
+        <v>モンブラン×2, プリンアラモード×1, Iceコーヒー×1, Iceココア×1, カフェオレ(Hot)×2, 午後の紅茶 ミルクティー×1</v>
+      </c>
+      <c r="E83">
+        <v>1600</v>
+      </c>
+      <c r="F83">
+        <v>300</v>
+      </c>
+      <c r="G83">
+        <v>1300</v>
+      </c>
+      <c r="H83">
+        <v>1300</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K83" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K83"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H223"/>
+  <dimension ref="A1:H229"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9079,9 +9114,165 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>#82</v>
+      </c>
+      <c r="B224" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C224" t="str">
+        <v>2026/9/26 12:30:07</v>
+      </c>
+      <c r="D224" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E224">
+        <v>200</v>
+      </c>
+      <c r="F224">
+        <v>2</v>
+      </c>
+      <c r="G224">
+        <v>400</v>
+      </c>
+      <c r="H224" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>#82</v>
+      </c>
+      <c r="B225" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C225" t="str">
+        <v>2026/9/26 12:30:07</v>
+      </c>
+      <c r="D225" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E225">
+        <v>200</v>
+      </c>
+      <c r="F225">
+        <v>1</v>
+      </c>
+      <c r="G225">
+        <v>200</v>
+      </c>
+      <c r="H225" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>#82</v>
+      </c>
+      <c r="B226" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C226" t="str">
+        <v>2026/9/26 12:30:07</v>
+      </c>
+      <c r="D226" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E226">
+        <v>200</v>
+      </c>
+      <c r="F226">
+        <v>1</v>
+      </c>
+      <c r="G226">
+        <v>200</v>
+      </c>
+      <c r="H226" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>#82</v>
+      </c>
+      <c r="B227" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C227" t="str">
+        <v>2026/9/26 12:30:07</v>
+      </c>
+      <c r="D227" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E227">
+        <v>200</v>
+      </c>
+      <c r="F227">
+        <v>1</v>
+      </c>
+      <c r="G227">
+        <v>200</v>
+      </c>
+      <c r="H227" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>#82</v>
+      </c>
+      <c r="B228" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C228" t="str">
+        <v>2026/9/26 12:30:07</v>
+      </c>
+      <c r="D228" t="str">
+        <v>カフェオレ(Hot)</v>
+      </c>
+      <c r="E228">
+        <v>200</v>
+      </c>
+      <c r="F228">
+        <v>2</v>
+      </c>
+      <c r="G228">
+        <v>400</v>
+      </c>
+      <c r="H228" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>#82</v>
+      </c>
+      <c r="B229" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C229" t="str">
+        <v>2026/9/26 12:30:07</v>
+      </c>
+      <c r="D229" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E229">
+        <v>200</v>
+      </c>
+      <c r="F229">
+        <v>1</v>
+      </c>
+      <c r="G229">
+        <v>200</v>
+      </c>
+      <c r="H229" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H223"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H229"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K83" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K85"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3305,16 +3305,86 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>#83</v>
+      </c>
+      <c r="B84" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C84" t="str">
+        <v>2026/9/26 12:35:32</v>
+      </c>
+      <c r="D84" t="str">
+        <v>クリームチーズタルト×3</v>
+      </c>
+      <c r="E84">
+        <v>600</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>600</v>
+      </c>
+      <c r="H84">
+        <v>600</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K84" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>#84</v>
+      </c>
+      <c r="B85" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C85" t="str">
+        <v>2026/9/26 12:36:31</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Iceコーヒー×3</v>
+      </c>
+      <c r="E85">
+        <v>600</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>600</v>
+      </c>
+      <c r="H85">
+        <v>1000</v>
+      </c>
+      <c r="I85">
+        <v>400</v>
+      </c>
+      <c r="J85" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K85" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K85"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H229"/>
+  <dimension ref="A1:H231"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9270,9 +9340,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>#83</v>
+      </c>
+      <c r="B230" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C230" t="str">
+        <v>2026/9/26 12:35:32</v>
+      </c>
+      <c r="D230" t="str">
+        <v>クリームチーズタルト</v>
+      </c>
+      <c r="E230">
+        <v>200</v>
+      </c>
+      <c r="F230">
+        <v>3</v>
+      </c>
+      <c r="G230">
+        <v>600</v>
+      </c>
+      <c r="H230" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>#84</v>
+      </c>
+      <c r="B231" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C231" t="str">
+        <v>2026/9/26 12:36:31</v>
+      </c>
+      <c r="D231" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E231">
+        <v>200</v>
+      </c>
+      <c r="F231">
+        <v>3</v>
+      </c>
+      <c r="G231">
+        <v>600</v>
+      </c>
+      <c r="H231" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H229"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H231"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -3369,7 +3369,7 @@
         <v>400</v>
       </c>
       <c r="J85" t="str">
-        <v>提供待ち</v>
+        <v>提供済み</v>
       </c>
       <c r="K85" t="str">
         <v>iti</v>

--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K87"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3375,16 +3375,86 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>#85</v>
+      </c>
+      <c r="B86" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C86" t="str">
+        <v>2026/9/26 12:38:07</v>
+      </c>
+      <c r="D86" t="str">
+        <v>モンブラン×1, Iceココア×1</v>
+      </c>
+      <c r="E86">
+        <v>400</v>
+      </c>
+      <c r="F86">
+        <v>100</v>
+      </c>
+      <c r="G86">
+        <v>300</v>
+      </c>
+      <c r="H86">
+        <v>300</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K86" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>#86</v>
+      </c>
+      <c r="B87" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C87" t="str">
+        <v>2026/9/26 12:39:05</v>
+      </c>
+      <c r="D87" t="str">
+        <v>モンブラン×1, オレンジジュース×1</v>
+      </c>
+      <c r="E87">
+        <v>400</v>
+      </c>
+      <c r="F87">
+        <v>100</v>
+      </c>
+      <c r="G87">
+        <v>300</v>
+      </c>
+      <c r="H87">
+        <v>300</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87" t="str">
+        <v>提供済み</v>
+      </c>
+      <c r="K87" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K85"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K87"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H231"/>
+  <dimension ref="A1:H235"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9392,9 +9462,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>#85</v>
+      </c>
+      <c r="B232" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C232" t="str">
+        <v>2026/9/26 12:38:07</v>
+      </c>
+      <c r="D232" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E232">
+        <v>200</v>
+      </c>
+      <c r="F232">
+        <v>1</v>
+      </c>
+      <c r="G232">
+        <v>200</v>
+      </c>
+      <c r="H232" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>#85</v>
+      </c>
+      <c r="B233" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C233" t="str">
+        <v>2026/9/26 12:38:07</v>
+      </c>
+      <c r="D233" t="str">
+        <v>Iceココア</v>
+      </c>
+      <c r="E233">
+        <v>200</v>
+      </c>
+      <c r="F233">
+        <v>1</v>
+      </c>
+      <c r="G233">
+        <v>200</v>
+      </c>
+      <c r="H233" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>#86</v>
+      </c>
+      <c r="B234" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C234" t="str">
+        <v>2026/9/26 12:39:05</v>
+      </c>
+      <c r="D234" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E234">
+        <v>200</v>
+      </c>
+      <c r="F234">
+        <v>1</v>
+      </c>
+      <c r="G234">
+        <v>200</v>
+      </c>
+      <c r="H234" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>#86</v>
+      </c>
+      <c r="B235" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C235" t="str">
+        <v>2026/9/26 12:39:05</v>
+      </c>
+      <c r="D235" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E235">
+        <v>200</v>
+      </c>
+      <c r="F235">
+        <v>1</v>
+      </c>
+      <c r="G235">
+        <v>200</v>
+      </c>
+      <c r="H235" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H231"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H235"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K92"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3445,16 +3445,191 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>#87</v>
+      </c>
+      <c r="B88" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C88" t="str">
+        <v>2026/9/26 12:43:04</v>
+      </c>
+      <c r="D88" t="str">
+        <v>カラメルカスタード×1, モンブラン×2, プリンアラモード×2, Ice紅茶×1, 午後の紅茶 ミルクティー×1, オレンジジュース×2</v>
+      </c>
+      <c r="E88">
+        <v>1800</v>
+      </c>
+      <c r="F88">
+        <v>400</v>
+      </c>
+      <c r="G88">
+        <v>1400</v>
+      </c>
+      <c r="H88">
+        <v>1400</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K88" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>#88</v>
+      </c>
+      <c r="B89" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C89" t="str">
+        <v>2026/9/26 12:44:20</v>
+      </c>
+      <c r="D89" t="str">
+        <v>プリンアラモード×1, Hotコーヒー×1, Iceコーヒー×1, Hotココア×1, オレンジジュース×1</v>
+      </c>
+      <c r="E89">
+        <v>1000</v>
+      </c>
+      <c r="F89">
+        <v>100</v>
+      </c>
+      <c r="G89">
+        <v>900</v>
+      </c>
+      <c r="H89">
+        <v>1000</v>
+      </c>
+      <c r="I89">
+        <v>100</v>
+      </c>
+      <c r="J89" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K89" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>#89</v>
+      </c>
+      <c r="B90" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C90" t="str">
+        <v>2026/9/26 12:45:25</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Iceコーヒー×2</v>
+      </c>
+      <c r="E90">
+        <v>400</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>400</v>
+      </c>
+      <c r="H90">
+        <v>400</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K90" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>#90</v>
+      </c>
+      <c r="B91" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C91" t="str">
+        <v>2026/9/26 12:46:37</v>
+      </c>
+      <c r="D91" t="str">
+        <v>モンブラン×2, Iceコーヒー×2</v>
+      </c>
+      <c r="E91">
+        <v>800</v>
+      </c>
+      <c r="F91">
+        <v>200</v>
+      </c>
+      <c r="G91">
+        <v>600</v>
+      </c>
+      <c r="H91">
+        <v>600</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K91" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>#91</v>
+      </c>
+      <c r="B92" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C92" t="str">
+        <v>2026/9/26 12:48:34</v>
+      </c>
+      <c r="D92" t="str">
+        <v>カラメルカスタード×2</v>
+      </c>
+      <c r="E92">
+        <v>400</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>400</v>
+      </c>
+      <c r="H92">
+        <v>1000</v>
+      </c>
+      <c r="I92">
+        <v>600</v>
+      </c>
+      <c r="J92" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K92" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K92"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H235"/>
+  <dimension ref="A1:H250"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9566,9 +9741,399 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>#87</v>
+      </c>
+      <c r="B236" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C236" t="str">
+        <v>2026/9/26 12:43:04</v>
+      </c>
+      <c r="D236" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E236">
+        <v>200</v>
+      </c>
+      <c r="F236">
+        <v>1</v>
+      </c>
+      <c r="G236">
+        <v>200</v>
+      </c>
+      <c r="H236" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>#87</v>
+      </c>
+      <c r="B237" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C237" t="str">
+        <v>2026/9/26 12:43:04</v>
+      </c>
+      <c r="D237" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E237">
+        <v>200</v>
+      </c>
+      <c r="F237">
+        <v>2</v>
+      </c>
+      <c r="G237">
+        <v>400</v>
+      </c>
+      <c r="H237" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>#87</v>
+      </c>
+      <c r="B238" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C238" t="str">
+        <v>2026/9/26 12:43:04</v>
+      </c>
+      <c r="D238" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E238">
+        <v>200</v>
+      </c>
+      <c r="F238">
+        <v>2</v>
+      </c>
+      <c r="G238">
+        <v>400</v>
+      </c>
+      <c r="H238" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>#87</v>
+      </c>
+      <c r="B239" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C239" t="str">
+        <v>2026/9/26 12:43:04</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E239">
+        <v>200</v>
+      </c>
+      <c r="F239">
+        <v>1</v>
+      </c>
+      <c r="G239">
+        <v>200</v>
+      </c>
+      <c r="H239" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>#87</v>
+      </c>
+      <c r="B240" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C240" t="str">
+        <v>2026/9/26 12:43:04</v>
+      </c>
+      <c r="D240" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E240">
+        <v>200</v>
+      </c>
+      <c r="F240">
+        <v>1</v>
+      </c>
+      <c r="G240">
+        <v>200</v>
+      </c>
+      <c r="H240" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>#87</v>
+      </c>
+      <c r="B241" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C241" t="str">
+        <v>2026/9/26 12:43:04</v>
+      </c>
+      <c r="D241" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E241">
+        <v>200</v>
+      </c>
+      <c r="F241">
+        <v>2</v>
+      </c>
+      <c r="G241">
+        <v>400</v>
+      </c>
+      <c r="H241" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>#88</v>
+      </c>
+      <c r="B242" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C242" t="str">
+        <v>2026/9/26 12:44:20</v>
+      </c>
+      <c r="D242" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E242">
+        <v>200</v>
+      </c>
+      <c r="F242">
+        <v>1</v>
+      </c>
+      <c r="G242">
+        <v>200</v>
+      </c>
+      <c r="H242" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>#88</v>
+      </c>
+      <c r="B243" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C243" t="str">
+        <v>2026/9/26 12:44:20</v>
+      </c>
+      <c r="D243" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E243">
+        <v>200</v>
+      </c>
+      <c r="F243">
+        <v>1</v>
+      </c>
+      <c r="G243">
+        <v>200</v>
+      </c>
+      <c r="H243" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>#88</v>
+      </c>
+      <c r="B244" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C244" t="str">
+        <v>2026/9/26 12:44:20</v>
+      </c>
+      <c r="D244" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E244">
+        <v>200</v>
+      </c>
+      <c r="F244">
+        <v>1</v>
+      </c>
+      <c r="G244">
+        <v>200</v>
+      </c>
+      <c r="H244" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>#88</v>
+      </c>
+      <c r="B245" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C245" t="str">
+        <v>2026/9/26 12:44:20</v>
+      </c>
+      <c r="D245" t="str">
+        <v>Hotココア</v>
+      </c>
+      <c r="E245">
+        <v>200</v>
+      </c>
+      <c r="F245">
+        <v>1</v>
+      </c>
+      <c r="G245">
+        <v>200</v>
+      </c>
+      <c r="H245" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>#88</v>
+      </c>
+      <c r="B246" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C246" t="str">
+        <v>2026/9/26 12:44:20</v>
+      </c>
+      <c r="D246" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E246">
+        <v>200</v>
+      </c>
+      <c r="F246">
+        <v>1</v>
+      </c>
+      <c r="G246">
+        <v>200</v>
+      </c>
+      <c r="H246" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>#89</v>
+      </c>
+      <c r="B247" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C247" t="str">
+        <v>2026/9/26 12:45:25</v>
+      </c>
+      <c r="D247" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E247">
+        <v>200</v>
+      </c>
+      <c r="F247">
+        <v>2</v>
+      </c>
+      <c r="G247">
+        <v>400</v>
+      </c>
+      <c r="H247" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>#90</v>
+      </c>
+      <c r="B248" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C248" t="str">
+        <v>2026/9/26 12:46:37</v>
+      </c>
+      <c r="D248" t="str">
+        <v>モンブラン</v>
+      </c>
+      <c r="E248">
+        <v>200</v>
+      </c>
+      <c r="F248">
+        <v>2</v>
+      </c>
+      <c r="G248">
+        <v>400</v>
+      </c>
+      <c r="H248" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>#90</v>
+      </c>
+      <c r="B249" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C249" t="str">
+        <v>2026/9/26 12:46:37</v>
+      </c>
+      <c r="D249" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E249">
+        <v>200</v>
+      </c>
+      <c r="F249">
+        <v>2</v>
+      </c>
+      <c r="G249">
+        <v>400</v>
+      </c>
+      <c r="H249" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>#91</v>
+      </c>
+      <c r="B250" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C250" t="str">
+        <v>2026/9/26 12:48:34</v>
+      </c>
+      <c r="D250" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E250">
+        <v>200</v>
+      </c>
+      <c r="F250">
+        <v>2</v>
+      </c>
+      <c r="G250">
+        <v>400</v>
+      </c>
+      <c r="H250" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H235"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H250"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K93"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3620,16 +3620,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>#92</v>
+      </c>
+      <c r="B93" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C93" t="str">
+        <v>2026/9/26 12:50:50</v>
+      </c>
+      <c r="D93" t="str">
+        <v>プリンアラモード×4, Iceコーヒー×2, カフェオレ(Hot)×1, オレンジジュース×1</v>
+      </c>
+      <c r="E93">
+        <v>1600</v>
+      </c>
+      <c r="F93">
+        <v>400</v>
+      </c>
+      <c r="G93">
+        <v>1200</v>
+      </c>
+      <c r="H93">
+        <v>1500</v>
+      </c>
+      <c r="I93">
+        <v>300</v>
+      </c>
+      <c r="J93" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K93" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K92"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K93"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H250"/>
+  <dimension ref="A1:H254"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10131,9 +10166,113 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>#92</v>
+      </c>
+      <c r="B251" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C251" t="str">
+        <v>2026/9/26 12:50:50</v>
+      </c>
+      <c r="D251" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E251">
+        <v>200</v>
+      </c>
+      <c r="F251">
+        <v>4</v>
+      </c>
+      <c r="G251">
+        <v>800</v>
+      </c>
+      <c r="H251" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>#92</v>
+      </c>
+      <c r="B252" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C252" t="str">
+        <v>2026/9/26 12:50:50</v>
+      </c>
+      <c r="D252" t="str">
+        <v>Iceコーヒー</v>
+      </c>
+      <c r="E252">
+        <v>200</v>
+      </c>
+      <c r="F252">
+        <v>2</v>
+      </c>
+      <c r="G252">
+        <v>400</v>
+      </c>
+      <c r="H252" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>#92</v>
+      </c>
+      <c r="B253" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C253" t="str">
+        <v>2026/9/26 12:50:50</v>
+      </c>
+      <c r="D253" t="str">
+        <v>カフェオレ(Hot)</v>
+      </c>
+      <c r="E253">
+        <v>200</v>
+      </c>
+      <c r="F253">
+        <v>1</v>
+      </c>
+      <c r="G253">
+        <v>200</v>
+      </c>
+      <c r="H253" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>#92</v>
+      </c>
+      <c r="B254" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C254" t="str">
+        <v>2026/9/26 12:50:50</v>
+      </c>
+      <c r="D254" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E254">
+        <v>200</v>
+      </c>
+      <c r="F254">
+        <v>1</v>
+      </c>
+      <c r="G254">
+        <v>200</v>
+      </c>
+      <c r="H254" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H250"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H254"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3655,16 +3655,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>#93</v>
+      </c>
+      <c r="B94" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C94" t="str">
+        <v>2026/9/26 12:54:00</v>
+      </c>
+      <c r="D94" t="str">
+        <v>カラメルカスタード×2, プリンアラモード×1, Hotココア×1</v>
+      </c>
+      <c r="E94">
+        <v>800</v>
+      </c>
+      <c r="F94">
+        <v>100</v>
+      </c>
+      <c r="G94">
+        <v>700</v>
+      </c>
+      <c r="H94">
+        <v>700</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K94" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K93"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K94"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H257"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10270,9 +10305,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>#93</v>
+      </c>
+      <c r="B255" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C255" t="str">
+        <v>2026/9/26 12:54:00</v>
+      </c>
+      <c r="D255" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E255">
+        <v>200</v>
+      </c>
+      <c r="F255">
+        <v>2</v>
+      </c>
+      <c r="G255">
+        <v>400</v>
+      </c>
+      <c r="H255" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>#93</v>
+      </c>
+      <c r="B256" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C256" t="str">
+        <v>2026/9/26 12:54:00</v>
+      </c>
+      <c r="D256" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E256">
+        <v>200</v>
+      </c>
+      <c r="F256">
+        <v>1</v>
+      </c>
+      <c r="G256">
+        <v>200</v>
+      </c>
+      <c r="H256" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>#93</v>
+      </c>
+      <c r="B257" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C257" t="str">
+        <v>2026/9/26 12:54:00</v>
+      </c>
+      <c r="D257" t="str">
+        <v>Hotココア</v>
+      </c>
+      <c r="E257">
+        <v>200</v>
+      </c>
+      <c r="F257">
+        <v>1</v>
+      </c>
+      <c r="G257">
+        <v>200</v>
+      </c>
+      <c r="H257" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H254"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H257"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3690,16 +3690,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>#94</v>
+      </c>
+      <c r="B95" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C95" t="str">
+        <v>2026/9/26 12:55:23</v>
+      </c>
+      <c r="D95" t="str">
+        <v>カラメルカスタード×3, カフェオレ(Hot)×3</v>
+      </c>
+      <c r="E95">
+        <v>1200</v>
+      </c>
+      <c r="F95">
+        <v>300</v>
+      </c>
+      <c r="G95">
+        <v>900</v>
+      </c>
+      <c r="H95">
+        <v>1000</v>
+      </c>
+      <c r="I95">
+        <v>100</v>
+      </c>
+      <c r="J95" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K95" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K95"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H257"/>
+  <dimension ref="A1:H259"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10383,9 +10418,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>#94</v>
+      </c>
+      <c r="B258" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C258" t="str">
+        <v>2026/9/26 12:55:23</v>
+      </c>
+      <c r="D258" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E258">
+        <v>200</v>
+      </c>
+      <c r="F258">
+        <v>3</v>
+      </c>
+      <c r="G258">
+        <v>600</v>
+      </c>
+      <c r="H258" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>#94</v>
+      </c>
+      <c r="B259" t="str">
+        <v>席 10</v>
+      </c>
+      <c r="C259" t="str">
+        <v>2026/9/26 12:55:23</v>
+      </c>
+      <c r="D259" t="str">
+        <v>カフェオレ(Hot)</v>
+      </c>
+      <c r="E259">
+        <v>200</v>
+      </c>
+      <c r="F259">
+        <v>3</v>
+      </c>
+      <c r="G259">
+        <v>600</v>
+      </c>
+      <c r="H259" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H257"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H259"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K96"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3725,16 +3725,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>#95</v>
+      </c>
+      <c r="B96" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C96" t="str">
+        <v>2026/9/26 12:56:51</v>
+      </c>
+      <c r="D96" t="str">
+        <v>カラメルカスタード×3, 午後の紅茶 ミルクティー×3</v>
+      </c>
+      <c r="E96">
+        <v>1200</v>
+      </c>
+      <c r="F96">
+        <v>300</v>
+      </c>
+      <c r="G96">
+        <v>900</v>
+      </c>
+      <c r="H96">
+        <v>1000</v>
+      </c>
+      <c r="I96">
+        <v>100</v>
+      </c>
+      <c r="J96" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K96" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K95"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K96"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H261"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10470,9 +10505,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>#95</v>
+      </c>
+      <c r="B260" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C260" t="str">
+        <v>2026/9/26 12:56:51</v>
+      </c>
+      <c r="D260" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E260">
+        <v>200</v>
+      </c>
+      <c r="F260">
+        <v>3</v>
+      </c>
+      <c r="G260">
+        <v>600</v>
+      </c>
+      <c r="H260" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>#95</v>
+      </c>
+      <c r="B261" t="str">
+        <v>席 9</v>
+      </c>
+      <c r="C261" t="str">
+        <v>2026/9/26 12:56:51</v>
+      </c>
+      <c r="D261" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E261">
+        <v>200</v>
+      </c>
+      <c r="F261">
+        <v>3</v>
+      </c>
+      <c r="G261">
+        <v>600</v>
+      </c>
+      <c r="H261" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H259"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H261"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3760,16 +3760,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>#96</v>
+      </c>
+      <c r="B97" t="str">
+        <v>席 11</v>
+      </c>
+      <c r="C97" t="str">
+        <v>2026/9/26 12:57:39</v>
+      </c>
+      <c r="D97" t="str">
+        <v>プリンアラモード×2, Ice紅茶×2</v>
+      </c>
+      <c r="E97">
+        <v>800</v>
+      </c>
+      <c r="F97">
+        <v>200</v>
+      </c>
+      <c r="G97">
+        <v>600</v>
+      </c>
+      <c r="H97">
+        <v>1000</v>
+      </c>
+      <c r="I97">
+        <v>400</v>
+      </c>
+      <c r="J97" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K97" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K96"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K97"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H261"/>
+  <dimension ref="A1:H263"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10557,9 +10592,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>#96</v>
+      </c>
+      <c r="B262" t="str">
+        <v>席 11</v>
+      </c>
+      <c r="C262" t="str">
+        <v>2026/9/26 12:57:39</v>
+      </c>
+      <c r="D262" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E262">
+        <v>200</v>
+      </c>
+      <c r="F262">
+        <v>2</v>
+      </c>
+      <c r="G262">
+        <v>400</v>
+      </c>
+      <c r="H262" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>#96</v>
+      </c>
+      <c r="B263" t="str">
+        <v>席 11</v>
+      </c>
+      <c r="C263" t="str">
+        <v>2026/9/26 12:57:39</v>
+      </c>
+      <c r="D263" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E263">
+        <v>200</v>
+      </c>
+      <c r="F263">
+        <v>2</v>
+      </c>
+      <c r="G263">
+        <v>400</v>
+      </c>
+      <c r="H263" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H261"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H263"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3795,16 +3795,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>#97</v>
+      </c>
+      <c r="B98" t="str">
+        <v>席 12</v>
+      </c>
+      <c r="C98" t="str">
+        <v>2026/9/26 12:58:14</v>
+      </c>
+      <c r="D98" t="str">
+        <v>カラメルカスタード×2, カフェオレ(Hot)×2</v>
+      </c>
+      <c r="E98">
+        <v>800</v>
+      </c>
+      <c r="F98">
+        <v>200</v>
+      </c>
+      <c r="G98">
+        <v>600</v>
+      </c>
+      <c r="H98">
+        <v>600</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K98" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K98"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H263"/>
+  <dimension ref="A1:H265"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10644,9 +10679,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>#97</v>
+      </c>
+      <c r="B264" t="str">
+        <v>席 12</v>
+      </c>
+      <c r="C264" t="str">
+        <v>2026/9/26 12:58:14</v>
+      </c>
+      <c r="D264" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E264">
+        <v>200</v>
+      </c>
+      <c r="F264">
+        <v>2</v>
+      </c>
+      <c r="G264">
+        <v>400</v>
+      </c>
+      <c r="H264" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>#97</v>
+      </c>
+      <c r="B265" t="str">
+        <v>席 12</v>
+      </c>
+      <c r="C265" t="str">
+        <v>2026/9/26 12:58:14</v>
+      </c>
+      <c r="D265" t="str">
+        <v>カフェオレ(Hot)</v>
+      </c>
+      <c r="E265">
+        <v>200</v>
+      </c>
+      <c r="F265">
+        <v>2</v>
+      </c>
+      <c r="G265">
+        <v>400</v>
+      </c>
+      <c r="H265" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H263"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H265"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K99"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3830,16 +3830,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>#98</v>
+      </c>
+      <c r="B99" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C99" t="str">
+        <v>2026/9/26 12:59:11</v>
+      </c>
+      <c r="D99" t="str">
+        <v>プリンアラモード×1, オレンジジュース×2</v>
+      </c>
+      <c r="E99">
+        <v>600</v>
+      </c>
+      <c r="F99">
+        <v>100</v>
+      </c>
+      <c r="G99">
+        <v>500</v>
+      </c>
+      <c r="H99">
+        <v>500</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K99" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K99"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H265"/>
+  <dimension ref="A1:H267"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10731,9 +10766,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>#98</v>
+      </c>
+      <c r="B266" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C266" t="str">
+        <v>2026/9/26 12:59:11</v>
+      </c>
+      <c r="D266" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E266">
+        <v>200</v>
+      </c>
+      <c r="F266">
+        <v>1</v>
+      </c>
+      <c r="G266">
+        <v>200</v>
+      </c>
+      <c r="H266" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>#98</v>
+      </c>
+      <c r="B267" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C267" t="str">
+        <v>2026/9/26 12:59:11</v>
+      </c>
+      <c r="D267" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E267">
+        <v>200</v>
+      </c>
+      <c r="F267">
+        <v>2</v>
+      </c>
+      <c r="G267">
+        <v>400</v>
+      </c>
+      <c r="H267" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H265"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H267"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:K100"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3865,16 +3865,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>#99</v>
+      </c>
+      <c r="B100" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C100" t="str">
+        <v>2026/9/26 12:59:51</v>
+      </c>
+      <c r="D100" t="str">
+        <v>プリンアラモード×2, Ice紅茶×2</v>
+      </c>
+      <c r="E100">
+        <v>800</v>
+      </c>
+      <c r="F100">
+        <v>200</v>
+      </c>
+      <c r="G100">
+        <v>600</v>
+      </c>
+      <c r="H100">
+        <v>600</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K100" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K100"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H267"/>
+  <dimension ref="A1:H269"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10818,9 +10853,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>#99</v>
+      </c>
+      <c r="B268" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C268" t="str">
+        <v>2026/9/26 12:59:51</v>
+      </c>
+      <c r="D268" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E268">
+        <v>200</v>
+      </c>
+      <c r="F268">
+        <v>2</v>
+      </c>
+      <c r="G268">
+        <v>400</v>
+      </c>
+      <c r="H268" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>#99</v>
+      </c>
+      <c r="B269" t="str">
+        <v>席 4</v>
+      </c>
+      <c r="C269" t="str">
+        <v>2026/9/26 12:59:51</v>
+      </c>
+      <c r="D269" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E269">
+        <v>200</v>
+      </c>
+      <c r="F269">
+        <v>2</v>
+      </c>
+      <c r="G269">
+        <v>400</v>
+      </c>
+      <c r="H269" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H267"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H269"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3900,16 +3900,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>#100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C101" t="str">
+        <v>2026/9/26 13:01:07</v>
+      </c>
+      <c r="D101" t="str">
+        <v>カラメルカスタード×2, Hot紅茶×2</v>
+      </c>
+      <c r="E101">
+        <v>800</v>
+      </c>
+      <c r="F101">
+        <v>200</v>
+      </c>
+      <c r="G101">
+        <v>600</v>
+      </c>
+      <c r="H101">
+        <v>1000</v>
+      </c>
+      <c r="I101">
+        <v>400</v>
+      </c>
+      <c r="J101" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K101" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K101"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H269"/>
+  <dimension ref="A1:H271"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10905,9 +10940,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>#100</v>
+      </c>
+      <c r="B270" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C270" t="str">
+        <v>2026/9/26 13:01:07</v>
+      </c>
+      <c r="D270" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E270">
+        <v>200</v>
+      </c>
+      <c r="F270">
+        <v>2</v>
+      </c>
+      <c r="G270">
+        <v>400</v>
+      </c>
+      <c r="H270" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>#100</v>
+      </c>
+      <c r="B271" t="str">
+        <v>席 8</v>
+      </c>
+      <c r="C271" t="str">
+        <v>2026/9/26 13:01:07</v>
+      </c>
+      <c r="D271" t="str">
+        <v>Hot紅茶</v>
+      </c>
+      <c r="E271">
+        <v>200</v>
+      </c>
+      <c r="F271">
+        <v>2</v>
+      </c>
+      <c r="G271">
+        <v>400</v>
+      </c>
+      <c r="H271" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H269"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H271"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3935,16 +3935,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>#101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C102" t="str">
+        <v>2026/9/26 13:04:57</v>
+      </c>
+      <c r="D102" t="str">
+        <v>カラメルカスタード×4, カフェオレ(Hot)×4</v>
+      </c>
+      <c r="E102">
+        <v>1600</v>
+      </c>
+      <c r="F102">
+        <v>400</v>
+      </c>
+      <c r="G102">
+        <v>1200</v>
+      </c>
+      <c r="H102">
+        <v>1200</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K102" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K102"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H271"/>
+  <dimension ref="A1:H273"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10992,9 +11027,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>#101</v>
+      </c>
+      <c r="B272" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C272" t="str">
+        <v>2026/9/26 13:04:57</v>
+      </c>
+      <c r="D272" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E272">
+        <v>200</v>
+      </c>
+      <c r="F272">
+        <v>4</v>
+      </c>
+      <c r="G272">
+        <v>800</v>
+      </c>
+      <c r="H272" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>#101</v>
+      </c>
+      <c r="B273" t="str">
+        <v>席 7</v>
+      </c>
+      <c r="C273" t="str">
+        <v>2026/9/26 13:04:57</v>
+      </c>
+      <c r="D273" t="str">
+        <v>カフェオレ(Hot)</v>
+      </c>
+      <c r="E273">
+        <v>200</v>
+      </c>
+      <c r="F273">
+        <v>4</v>
+      </c>
+      <c r="G273">
+        <v>800</v>
+      </c>
+      <c r="H273" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H271"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H273"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3970,16 +3970,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>#102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C103" t="str">
+        <v>2026/9/26 13:09:29</v>
+      </c>
+      <c r="D103" t="str">
+        <v>プリンアラモード×2, Ice紅茶×1, 午後の紅茶 ミルクティー×1</v>
+      </c>
+      <c r="E103">
+        <v>800</v>
+      </c>
+      <c r="F103">
+        <v>200</v>
+      </c>
+      <c r="G103">
+        <v>600</v>
+      </c>
+      <c r="H103">
+        <v>1000</v>
+      </c>
+      <c r="I103">
+        <v>400</v>
+      </c>
+      <c r="J103" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K103" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K103"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H273"/>
+  <dimension ref="A1:H276"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11079,9 +11114,87 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>#102</v>
+      </c>
+      <c r="B274" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C274" t="str">
+        <v>2026/9/26 13:09:29</v>
+      </c>
+      <c r="D274" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E274">
+        <v>200</v>
+      </c>
+      <c r="F274">
+        <v>2</v>
+      </c>
+      <c r="G274">
+        <v>400</v>
+      </c>
+      <c r="H274" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>#102</v>
+      </c>
+      <c r="B275" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C275" t="str">
+        <v>2026/9/26 13:09:29</v>
+      </c>
+      <c r="D275" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E275">
+        <v>200</v>
+      </c>
+      <c r="F275">
+        <v>1</v>
+      </c>
+      <c r="G275">
+        <v>200</v>
+      </c>
+      <c r="H275" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>#102</v>
+      </c>
+      <c r="B276" t="str">
+        <v>席 1</v>
+      </c>
+      <c r="C276" t="str">
+        <v>2026/9/26 13:09:29</v>
+      </c>
+      <c r="D276" t="str">
+        <v>午後の紅茶 ミルクティー</v>
+      </c>
+      <c r="E276">
+        <v>200</v>
+      </c>
+      <c r="F276">
+        <v>1</v>
+      </c>
+      <c r="G276">
+        <v>200</v>
+      </c>
+      <c r="H276" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H273"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H276"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K104"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4005,16 +4005,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>#103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C104" t="str">
+        <v>2026/9/26 13:11:25</v>
+      </c>
+      <c r="D104" t="str">
+        <v>カラメルカスタード×2, オレンジジュース×1</v>
+      </c>
+      <c r="E104">
+        <v>600</v>
+      </c>
+      <c r="F104">
+        <v>100</v>
+      </c>
+      <c r="G104">
+        <v>500</v>
+      </c>
+      <c r="H104">
+        <v>500</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K104" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K104"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H278"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11192,9 +11227,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>#103</v>
+      </c>
+      <c r="B277" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C277" t="str">
+        <v>2026/9/26 13:11:25</v>
+      </c>
+      <c r="D277" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E277">
+        <v>200</v>
+      </c>
+      <c r="F277">
+        <v>2</v>
+      </c>
+      <c r="G277">
+        <v>400</v>
+      </c>
+      <c r="H277" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>#103</v>
+      </c>
+      <c r="B278" t="str">
+        <v>席 2</v>
+      </c>
+      <c r="C278" t="str">
+        <v>2026/9/26 13:11:25</v>
+      </c>
+      <c r="D278" t="str">
+        <v>オレンジジュース</v>
+      </c>
+      <c r="E278">
+        <v>200</v>
+      </c>
+      <c r="F278">
+        <v>1</v>
+      </c>
+      <c r="G278">
+        <v>200</v>
+      </c>
+      <c r="H278" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H276"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H278"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4040,16 +4040,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>#104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C105" t="str">
+        <v>2026/9/26 13:12:58</v>
+      </c>
+      <c r="D105" t="str">
+        <v>プリンアラモード×1, Hotココア×1</v>
+      </c>
+      <c r="E105">
+        <v>400</v>
+      </c>
+      <c r="F105">
+        <v>100</v>
+      </c>
+      <c r="G105">
+        <v>300</v>
+      </c>
+      <c r="H105">
+        <v>300</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K105" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K104"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K105"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H278"/>
+  <dimension ref="A1:H280"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11279,9 +11314,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>#104</v>
+      </c>
+      <c r="B279" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C279" t="str">
+        <v>2026/9/26 13:12:58</v>
+      </c>
+      <c r="D279" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E279">
+        <v>200</v>
+      </c>
+      <c r="F279">
+        <v>1</v>
+      </c>
+      <c r="G279">
+        <v>200</v>
+      </c>
+      <c r="H279" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>#104</v>
+      </c>
+      <c r="B280" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C280" t="str">
+        <v>2026/9/26 13:12:58</v>
+      </c>
+      <c r="D280" t="str">
+        <v>Hotココア</v>
+      </c>
+      <c r="E280">
+        <v>200</v>
+      </c>
+      <c r="F280">
+        <v>1</v>
+      </c>
+      <c r="G280">
+        <v>200</v>
+      </c>
+      <c r="H280" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H278"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H280"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K106"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4075,16 +4075,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>#105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C106" t="str">
+        <v>2026/9/26 13:14:58</v>
+      </c>
+      <c r="D106" t="str">
+        <v>プリンアラモード×1, Hotココア×1</v>
+      </c>
+      <c r="E106">
+        <v>400</v>
+      </c>
+      <c r="F106">
+        <v>100</v>
+      </c>
+      <c r="G106">
+        <v>300</v>
+      </c>
+      <c r="H106">
+        <v>300</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K106" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K106"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H280"/>
+  <dimension ref="A1:H282"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11366,9 +11401,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>#105</v>
+      </c>
+      <c r="B281" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C281" t="str">
+        <v>2026/9/26 13:14:58</v>
+      </c>
+      <c r="D281" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E281">
+        <v>200</v>
+      </c>
+      <c r="F281">
+        <v>1</v>
+      </c>
+      <c r="G281">
+        <v>200</v>
+      </c>
+      <c r="H281" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>#105</v>
+      </c>
+      <c r="B282" t="str">
+        <v>席 15</v>
+      </c>
+      <c r="C282" t="str">
+        <v>2026/9/26 13:14:58</v>
+      </c>
+      <c r="D282" t="str">
+        <v>Hotココア</v>
+      </c>
+      <c r="E282">
+        <v>200</v>
+      </c>
+      <c r="F282">
+        <v>1</v>
+      </c>
+      <c r="G282">
+        <v>200</v>
+      </c>
+      <c r="H282" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H280"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H282"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K107"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4110,16 +4110,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>#106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C107" t="str">
+        <v>2026/9/26 13:16:18</v>
+      </c>
+      <c r="D107" t="str">
+        <v>プリンアラモード×1, Hotコーヒー×1</v>
+      </c>
+      <c r="E107">
+        <v>400</v>
+      </c>
+      <c r="F107">
+        <v>100</v>
+      </c>
+      <c r="G107">
+        <v>300</v>
+      </c>
+      <c r="H107">
+        <v>1000</v>
+      </c>
+      <c r="I107">
+        <v>700</v>
+      </c>
+      <c r="J107" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K107" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K106"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K107"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H282"/>
+  <dimension ref="A1:H284"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11453,9 +11488,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>#106</v>
+      </c>
+      <c r="B283" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C283" t="str">
+        <v>2026/9/26 13:16:18</v>
+      </c>
+      <c r="D283" t="str">
+        <v>プリンアラモード</v>
+      </c>
+      <c r="E283">
+        <v>200</v>
+      </c>
+      <c r="F283">
+        <v>1</v>
+      </c>
+      <c r="G283">
+        <v>200</v>
+      </c>
+      <c r="H283" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>#106</v>
+      </c>
+      <c r="B284" t="str">
+        <v>席 3</v>
+      </c>
+      <c r="C284" t="str">
+        <v>2026/9/26 13:16:18</v>
+      </c>
+      <c r="D284" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E284">
+        <v>200</v>
+      </c>
+      <c r="F284">
+        <v>1</v>
+      </c>
+      <c r="G284">
+        <v>200</v>
+      </c>
+      <c r="H284" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H282"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H284"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K108"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4145,16 +4145,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>#107</v>
+      </c>
+      <c r="B108" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C108" t="str">
+        <v>2026/9/26 13:16:51</v>
+      </c>
+      <c r="D108" t="str">
+        <v>カラメルカスタード×2, Hotコーヒー×2</v>
+      </c>
+      <c r="E108">
+        <v>800</v>
+      </c>
+      <c r="F108">
+        <v>200</v>
+      </c>
+      <c r="G108">
+        <v>600</v>
+      </c>
+      <c r="H108">
+        <v>600</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K108" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K107"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H284"/>
+  <dimension ref="A1:H286"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11540,9 +11575,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>#107</v>
+      </c>
+      <c r="B285" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C285" t="str">
+        <v>2026/9/26 13:16:51</v>
+      </c>
+      <c r="D285" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E285">
+        <v>200</v>
+      </c>
+      <c r="F285">
+        <v>2</v>
+      </c>
+      <c r="G285">
+        <v>400</v>
+      </c>
+      <c r="H285" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>#107</v>
+      </c>
+      <c r="B286" t="str">
+        <v>席 5</v>
+      </c>
+      <c r="C286" t="str">
+        <v>2026/9/26 13:16:51</v>
+      </c>
+      <c r="D286" t="str">
+        <v>Hotコーヒー</v>
+      </c>
+      <c r="E286">
+        <v>200</v>
+      </c>
+      <c r="F286">
+        <v>2</v>
+      </c>
+      <c r="G286">
+        <v>400</v>
+      </c>
+      <c r="H286" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H284"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H286"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sales_log.xlsx
+++ b/sales_log.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K109"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4180,16 +4180,51 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>#108</v>
+      </c>
+      <c r="B109" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C109" t="str">
+        <v>2026/9/26 13:22:29</v>
+      </c>
+      <c r="D109" t="str">
+        <v>カラメルカスタード×1, Ice紅茶×1</v>
+      </c>
+      <c r="E109">
+        <v>400</v>
+      </c>
+      <c r="F109">
+        <v>100</v>
+      </c>
+      <c r="G109">
+        <v>300</v>
+      </c>
+      <c r="H109">
+        <v>500</v>
+      </c>
+      <c r="I109">
+        <v>200</v>
+      </c>
+      <c r="J109" t="str">
+        <v>提供待ち</v>
+      </c>
+      <c r="K109" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K109"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H286"/>
+  <dimension ref="A1:H288"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11627,9 +11662,61 @@
         <v>iti</v>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>#108</v>
+      </c>
+      <c r="B287" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C287" t="str">
+        <v>2026/9/26 13:22:29</v>
+      </c>
+      <c r="D287" t="str">
+        <v>カラメルカスタード</v>
+      </c>
+      <c r="E287">
+        <v>200</v>
+      </c>
+      <c r="F287">
+        <v>1</v>
+      </c>
+      <c r="G287">
+        <v>200</v>
+      </c>
+      <c r="H287" t="str">
+        <v>iti</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>#108</v>
+      </c>
+      <c r="B288" t="str">
+        <v>席 6</v>
+      </c>
+      <c r="C288" t="str">
+        <v>2026/9/26 13:22:29</v>
+      </c>
+      <c r="D288" t="str">
+        <v>Ice紅茶</v>
+      </c>
+      <c r="E288">
+        <v>200</v>
+      </c>
+      <c r="F288">
+        <v>1</v>
+      </c>
+      <c r="G288">
+        <v>200</v>
+      </c>
+      <c r="H288" t="str">
+        <v>iti</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H286"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H288"/>
   </ignoredErrors>
 </worksheet>
 </file>